--- a/data/SEMANA ATUAL/rodada 8/BIOFRESH.xlsx
+++ b/data/SEMANA ATUAL/rodada 8/BIOFRESH.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="277">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -34,9 +34,21 @@
     <t>20/08/2026 (Qui)</t>
   </si>
   <si>
+    <t>21/08/2026 (Sex)</t>
+  </si>
+  <si>
+    <t>22/08/2026 (Sáb)</t>
+  </si>
+  <si>
+    <t>23/08/2026 (Dom)</t>
+  </si>
+  <si>
     <t>ABNO-RJ</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>ABVT-SP</t>
   </si>
   <si>
@@ -61,9 +73,6 @@
     <t>AEST-SP</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>AFCO-SP</t>
   </si>
   <si>
@@ -638,6 +647,9 @@
   </si>
   <si>
     <t>RPIN-SP</t>
+  </si>
+  <si>
+    <t>RPTO-SP</t>
   </si>
   <si>
     <t>RPVG-SP</t>
@@ -1198,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:I268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1206,7 +1218,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1225,13 +1237,22 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
-        <v>801.1400000000001</v>
+        <v>801.14</v>
       </c>
       <c r="D2" s="1">
         <v>1728.57</v>
@@ -1242,10 +1263,19 @@
       <c r="F2" s="1">
         <v>709.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>811.48</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1370.68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>494.99</v>
@@ -1259,10 +1289,19 @@
       <c r="F3" s="1">
         <v>1111.18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>-82.92999999999998</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1245.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>366.49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>2193.38</v>
@@ -1274,12 +1313,21 @@
         <v>1565.16</v>
       </c>
       <c r="F4" s="1">
-        <v>3331.44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3331.439999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>811.52</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2644.45</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1991.72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>1186.42</v>
@@ -1293,10 +1341,19 @@
       <c r="F5" s="1">
         <v>876.04</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1">
+        <v>1266.56</v>
+      </c>
+      <c r="H5" s="1">
+        <v>484.29</v>
+      </c>
+      <c r="I5" s="1">
+        <v>630.89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
         <v>809.1399999999999</v>
@@ -1310,10 +1367,19 @@
       <c r="F6" s="1">
         <v>1849.58</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1">
+        <v>681.8</v>
+      </c>
+      <c r="H6" s="1">
+        <v>744.46</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1614.61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>834.47</v>
@@ -1327,10 +1393,19 @@
       <c r="F7" s="1">
         <v>1346.85</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="1">
+        <v>128.71</v>
+      </c>
+      <c r="H7" s="1">
+        <v>495.23</v>
+      </c>
+      <c r="I7" s="1">
+        <v>190.93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>337.48</v>
@@ -1344,10 +1419,19 @@
       <c r="F8" s="1">
         <v>85.23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1">
+        <v>2.66</v>
+      </c>
+      <c r="H8" s="1">
+        <v>153.99</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1088.28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>578.0700000000001</v>
@@ -1361,16 +1445,25 @@
       <c r="F9" s="1">
         <v>1298.39</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1">
+        <v>1951.15</v>
+      </c>
+      <c r="H9" s="1">
+        <v>504.73</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1184.53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1">
         <v>666.8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1">
         <v>195.39</v>
@@ -1378,10 +1471,19 @@
       <c r="F10" s="1">
         <v>918.85</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1">
+        <v>77.81</v>
+      </c>
+      <c r="H10" s="1">
+        <v>531.54</v>
+      </c>
+      <c r="I10" s="1">
+        <v>353.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>1148.76</v>
@@ -1395,10 +1497,19 @@
       <c r="F11" s="1">
         <v>1017.44</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="1">
+        <v>739.5599999999999</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1133.95</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1824.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1">
         <v>1055.99</v>
@@ -1412,10 +1523,19 @@
       <c r="F12" s="1">
         <v>273.06</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1">
+        <v>414.13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>457.69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1">
         <v>249.61</v>
@@ -1429,10 +1549,19 @@
       <c r="F13" s="1">
         <v>1354.19</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="1">
+        <v>1040.49</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1192.46</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1259.68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>1355.38</v>
@@ -1446,10 +1575,19 @@
       <c r="F14" s="1">
         <v>428.64</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="1">
+        <v>511.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>290.79</v>
+      </c>
+      <c r="I14" s="1">
+        <v>700.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1">
         <v>1938.94</v>
@@ -1463,10 +1601,19 @@
       <c r="F15" s="1">
         <v>1029.3</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="1">
+        <v>2513.06</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1464.79</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1939.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1">
         <v>225.05</v>
@@ -1478,12 +1625,21 @@
         <v>467</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>614.97</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>350.97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1">
         <v>1014.36</v>
@@ -1497,13 +1653,22 @@
       <c r="F17" s="1">
         <v>504.56</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="1">
+        <v>700.97</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1770.16</v>
+      </c>
+      <c r="I17" s="1">
+        <v>933.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1">
         <v>924.4000000000001</v>
@@ -1512,12 +1677,21 @@
         <v>1475.25</v>
       </c>
       <c r="F18" s="1">
-        <v>481.67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>481.6700000000001</v>
+      </c>
+      <c r="G18" s="1">
+        <v>120.49</v>
+      </c>
+      <c r="H18" s="1">
+        <v>749.98</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1">
         <v>794.26</v>
@@ -1529,12 +1703,21 @@
         <v>794.37</v>
       </c>
       <c r="F19" s="1">
-        <v>795.5300000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>795.53</v>
+      </c>
+      <c r="G19" s="1">
+        <v>386.97</v>
+      </c>
+      <c r="H19" s="1">
+        <v>680.5300000000001</v>
+      </c>
+      <c r="I19" s="1">
+        <v>542.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
         <v>633.98</v>
@@ -1548,13 +1731,22 @@
       <c r="F20" s="1">
         <v>472.98</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="1">
+        <v>224.99</v>
+      </c>
+      <c r="H20" s="1">
+        <v>428.3100000000001</v>
+      </c>
+      <c r="I20" s="1">
+        <v>834.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1">
         <v>699.98</v>
@@ -1565,16 +1757,25 @@
       <c r="F21" s="1">
         <v>784.78</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1">
+        <v>304.97</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="1">
+        <v>397.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1">
         <v>810.79</v>
@@ -1582,13 +1783,22 @@
       <c r="F22" s="1">
         <v>138.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1">
         <v>199.99</v>
@@ -1599,16 +1809,25 @@
       <c r="F23" s="1">
         <v>643.77</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="1">
+        <v>1587.28</v>
+      </c>
+      <c r="H23" s="1">
+        <v>303.3</v>
+      </c>
+      <c r="I23" s="1">
+        <v>589.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1">
         <v>86.98999999999999</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1">
         <v>87.39</v>
@@ -1616,10 +1835,19 @@
       <c r="F24" s="1">
         <v>649.8099999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1">
+        <v>651.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>488.29</v>
+      </c>
+      <c r="I24" s="1">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
         <v>2399.03</v>
@@ -1633,10 +1861,19 @@
       <c r="F25" s="1">
         <v>1937.04</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1">
+        <v>1096</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1786.02</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1256.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1">
         <v>481.14</v>
@@ -1650,10 +1887,19 @@
       <c r="F26" s="1">
         <v>354.99</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="1">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="H26" s="1">
+        <v>662.02</v>
+      </c>
+      <c r="I26" s="1">
+        <v>704.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1">
         <v>631.1700000000001</v>
@@ -1667,10 +1913,19 @@
       <c r="F27" s="1">
         <v>890.6799999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1">
+        <v>519.48</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1415.62</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1165.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
         <v>1359.63</v>
@@ -1684,16 +1939,25 @@
       <c r="F28" s="1">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1">
+        <v>1212.94</v>
+      </c>
+      <c r="H28" s="1">
+        <v>718.9200000000001</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1179.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1">
         <v>423.85</v>
       </c>
       <c r="D29" s="1">
-        <v>861.4799999999999</v>
+        <v>861.48</v>
       </c>
       <c r="E29" s="1">
         <v>1177.71</v>
@@ -1701,10 +1965,19 @@
       <c r="F29" s="1">
         <v>915</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="1">
+        <v>1400.06</v>
+      </c>
+      <c r="H29" s="1">
+        <v>283.08</v>
+      </c>
+      <c r="I29" s="1">
+        <v>651.1799999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
         <v>181.46</v>
@@ -1716,12 +1989,21 @@
         <v>279.76</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1103.96</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1">
+        <v>588.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
         <v>1332.93</v>
@@ -1735,10 +2017,19 @@
       <c r="F31" s="1">
         <v>2353.78</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="1">
+        <v>2367.65</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2490.21</v>
+      </c>
+      <c r="I31" s="1">
+        <v>244.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C32" s="1">
         <v>3937.310000000001</v>
@@ -1752,10 +2043,19 @@
       <c r="F32" s="1">
         <v>991</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="1">
+        <v>1529.32</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2776.92</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1552.46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1">
         <v>1526.33</v>
@@ -1764,15 +2064,24 @@
         <v>1830.69</v>
       </c>
       <c r="E33" s="1">
-        <v>986.2199999999999</v>
+        <v>986.22</v>
       </c>
       <c r="F33" s="1">
         <v>399.98</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="1">
+        <v>2007.79</v>
+      </c>
+      <c r="H33" s="1">
+        <v>717.9200000000001</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1995.52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C34" s="1">
         <v>444.29</v>
@@ -1786,10 +2095,19 @@
       <c r="F34" s="1">
         <v>179.99</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="1">
+        <v>233.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1">
         <v>1712.18</v>
@@ -1803,10 +2121,19 @@
       <c r="F35" s="1">
         <v>319.02</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="1">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1222.86</v>
+      </c>
+      <c r="I35" s="1">
+        <v>748.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1">
         <v>1924.4</v>
@@ -1818,18 +2145,27 @@
         <v>2023.9</v>
       </c>
       <c r="F36" s="1">
-        <v>4511.879999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>4511.88</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1817.57</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2040.59</v>
+      </c>
+      <c r="I36" s="1">
+        <v>433.78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1">
         <v>470.64</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E37" s="1">
         <v>132.98</v>
@@ -1837,10 +2173,19 @@
       <c r="F37" s="1">
         <v>484.48</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="1">
+        <v>368.11</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" s="1">
+        <v>249.49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1">
         <v>282.98</v>
@@ -1854,10 +2199,19 @@
       <c r="F38" s="1">
         <v>233.39</v>
       </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="1">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="H38" s="1">
+        <v>452.97</v>
+      </c>
+      <c r="I38" s="1">
+        <v>227.59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C39" s="1">
         <v>1182.97</v>
@@ -1871,10 +2225,19 @@
       <c r="F39" s="1">
         <v>538.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="1">
+        <v>645.61</v>
+      </c>
+      <c r="H39" s="1">
+        <v>658.25</v>
+      </c>
+      <c r="I39" s="1">
+        <v>514.0599999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C40" s="1">
         <v>1015.29</v>
@@ -1888,10 +2251,19 @@
       <c r="F40" s="1">
         <v>976.5899999999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="1">
+        <v>441.8100000000001</v>
+      </c>
+      <c r="H40" s="1">
+        <v>768.8800000000001</v>
+      </c>
+      <c r="I40" s="1">
+        <v>223.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1">
         <v>2232.39</v>
@@ -1903,15 +2275,24 @@
         <v>421.02</v>
       </c>
       <c r="F41" s="1">
-        <v>595.8699999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>595.8700000000001</v>
+      </c>
+      <c r="G41" s="1">
+        <v>404.48</v>
+      </c>
+      <c r="H41" s="1">
+        <v>197.62</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1031.97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D42" s="1">
         <v>85.8</v>
@@ -1922,13 +2303,22 @@
       <c r="F42" s="1">
         <v>380.98</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="1">
+        <v>259.99</v>
+      </c>
+      <c r="H42" s="1">
+        <v>151.98</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1">
-        <v>896.5400000000001</v>
+        <v>896.54</v>
       </c>
       <c r="D43" s="1">
         <v>2410.8</v>
@@ -1939,10 +2329,19 @@
       <c r="F43" s="1">
         <v>874.97</v>
       </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="1">
+        <v>555.34</v>
+      </c>
+      <c r="H43" s="1">
+        <v>945.8</v>
+      </c>
+      <c r="I43" s="1">
+        <v>940.3099999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1">
         <v>1729.62</v>
@@ -1956,10 +2355,19 @@
       <c r="F44" s="1">
         <v>1153.36</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="1">
+        <v>319.49</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1036.39</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1242.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C45" s="1">
         <v>657.6999999999998</v>
@@ -1973,10 +2381,19 @@
       <c r="F45" s="1">
         <v>959.27</v>
       </c>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="1">
+        <v>2416.19</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2064.53</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1863.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C46" s="1">
         <v>180.49</v>
@@ -1990,10 +2407,19 @@
       <c r="F46" s="1">
         <v>786.96</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="1">
+        <v>840.79</v>
+      </c>
+      <c r="H46" s="1">
+        <v>45.99</v>
+      </c>
+      <c r="I46" s="1">
+        <v>904.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C47" s="1">
         <v>1255.44</v>
@@ -2005,15 +2431,24 @@
         <v>1276.67</v>
       </c>
       <c r="F47" s="1">
-        <v>690.0799999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>690.08</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1462.58</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2120.9</v>
+      </c>
+      <c r="I47" s="1">
+        <v>2228.73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C48" s="1">
-        <v>925.84</v>
+        <v>925.8400000000001</v>
       </c>
       <c r="D48" s="1">
         <v>644.4</v>
@@ -2024,10 +2459,19 @@
       <c r="F48" s="1">
         <v>827.71</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="1">
+        <v>1098.82</v>
+      </c>
+      <c r="H48" s="1">
+        <v>661.8</v>
+      </c>
+      <c r="I48" s="1">
+        <v>259.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C49" s="1">
         <v>837.8200000000001</v>
@@ -2036,15 +2480,24 @@
         <v>1351.15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F49" s="1">
         <v>204.98</v>
       </c>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="1">
+        <v>653.36</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="1">
+        <v>12.75999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C50" s="1">
         <v>875.75</v>
@@ -2058,16 +2511,25 @@
       <c r="F50" s="1">
         <v>209.08</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="1">
+        <v>191.99</v>
+      </c>
+      <c r="H50" s="1">
+        <v>-287.97</v>
+      </c>
+      <c r="I50" s="1">
+        <v>182.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E51" s="1">
         <v>272.8</v>
@@ -2075,10 +2537,19 @@
       <c r="F51" s="1">
         <v>1133.37</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="1">
+        <v>492.98</v>
+      </c>
+      <c r="H51" s="1">
+        <v>542.3</v>
+      </c>
+      <c r="I51" s="1">
+        <v>288.13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1">
         <v>1254.94</v>
@@ -2092,13 +2563,22 @@
       <c r="F52" s="1">
         <v>446.4399999999999</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="1">
+        <v>92.05999999999999</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1076.19</v>
+      </c>
+      <c r="I52" s="1">
+        <v>320.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D53" s="1">
         <v>283.19</v>
@@ -2109,10 +2589,19 @@
       <c r="F53" s="1">
         <v>389.6500000000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="1">
+        <v>543.64</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1">
         <v>328.98</v>
@@ -2126,10 +2615,19 @@
       <c r="F54" s="1">
         <v>176.48</v>
       </c>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="1">
+        <v>2343.88</v>
+      </c>
+      <c r="H54" s="1">
+        <v>302.58</v>
+      </c>
+      <c r="I54" s="1">
+        <v>347.98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C55" s="1">
         <v>1271.28</v>
@@ -2143,16 +2641,25 @@
       <c r="F55" s="1">
         <v>355.99</v>
       </c>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="1">
+        <v>384.78</v>
+      </c>
+      <c r="H55" s="1">
+        <v>531.14</v>
+      </c>
+      <c r="I55" s="1">
+        <v>115.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C56" s="1">
         <v>4586.339999999999</v>
       </c>
       <c r="D56" s="1">
-        <v>4204.369999999999</v>
+        <v>4204.37</v>
       </c>
       <c r="E56" s="1">
         <v>4180.29</v>
@@ -2160,10 +2667,19 @@
       <c r="F56" s="1">
         <v>4900.82</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="1">
+        <v>3562.18</v>
+      </c>
+      <c r="H56" s="1">
+        <v>4900.139999999999</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1">
         <v>745.49</v>
@@ -2177,10 +2693,19 @@
       <c r="F57" s="1">
         <v>227.91</v>
       </c>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="1">
+        <v>778.88</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1107.28</v>
+      </c>
+      <c r="I57" s="1">
+        <v>737.6900000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C58" s="1">
         <v>819.98</v>
@@ -2194,16 +2719,25 @@
       <c r="F58" s="1">
         <v>269.98</v>
       </c>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="1">
+        <v>2068.37</v>
+      </c>
+      <c r="H58" s="1">
+        <v>171</v>
+      </c>
+      <c r="I58" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E59" s="1">
         <v>148.13</v>
@@ -2211,16 +2745,25 @@
       <c r="F59" s="1">
         <v>81</v>
       </c>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="1">
+        <v>664.98</v>
+      </c>
+      <c r="H59" s="1">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="I59" s="1">
+        <v>257.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1">
         <v>1130.64</v>
       </c>
       <c r="D60" s="1">
-        <v>530.0899999999999</v>
+        <v>530.09</v>
       </c>
       <c r="E60" s="1">
         <v>1598.37</v>
@@ -2228,10 +2771,19 @@
       <c r="F60" s="1">
         <v>1514.24</v>
       </c>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="1">
+        <v>604.6799999999999</v>
+      </c>
+      <c r="H60" s="1">
+        <v>864.5599999999999</v>
+      </c>
+      <c r="I60" s="1">
+        <v>894.96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C61" s="1">
         <v>86.98999999999999</v>
@@ -2245,10 +2797,19 @@
       <c r="F61" s="1">
         <v>554.98</v>
       </c>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" s="1">
+        <v>601.98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C62" s="1">
         <v>656.8200000000001</v>
@@ -2262,10 +2823,19 @@
       <c r="F62" s="1">
         <v>1074.92</v>
       </c>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="1">
+        <v>1571.58</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1943.96</v>
+      </c>
+      <c r="I62" s="1">
+        <v>1040.14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C63" s="1">
         <v>45.99</v>
@@ -2279,13 +2849,22 @@
       <c r="F63" s="1">
         <v>954.85</v>
       </c>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="1">
+        <v>485.98</v>
+      </c>
+      <c r="H63" s="1">
+        <v>40.49</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D64" s="1">
         <v>297.16</v>
@@ -2296,13 +2875,22 @@
       <c r="F64" s="1">
         <v>266.64</v>
       </c>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="1">
+        <v>402.01</v>
+      </c>
+      <c r="H64" s="1">
+        <v>199.99</v>
+      </c>
+      <c r="I64" s="1">
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D65" s="1">
         <v>575.4200000000001</v>
@@ -2313,10 +2901,19 @@
       <c r="F65" s="1">
         <v>184.59</v>
       </c>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="1">
+        <v>574.1400000000001</v>
+      </c>
+      <c r="H65" s="1">
+        <v>126.39</v>
+      </c>
+      <c r="I65" s="1">
+        <v>292.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="1">
         <v>786.2</v>
@@ -2330,10 +2927,19 @@
       <c r="F66" s="1">
         <v>166.38</v>
       </c>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="1">
+        <v>628.24</v>
+      </c>
+      <c r="H66" s="1">
+        <v>266.82</v>
+      </c>
+      <c r="I66" s="1">
+        <v>91.79000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C67" s="1">
         <v>978.2099999999999</v>
@@ -2342,15 +2948,24 @@
         <v>481.88</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F67" s="1">
         <v>829.53</v>
       </c>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="1">
+        <v>440.67</v>
+      </c>
+      <c r="H67" s="1">
+        <v>874.97</v>
+      </c>
+      <c r="I67" s="1">
+        <v>571.6900000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1">
         <v>851.77</v>
@@ -2362,12 +2977,21 @@
         <v>361.98</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="1">
+        <v>144.41</v>
+      </c>
+      <c r="I68" s="1">
+        <v>1013.13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C69" s="1">
         <v>823.4299999999999</v>
@@ -2381,16 +3005,25 @@
       <c r="F69" s="1">
         <v>1526.94</v>
       </c>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="1">
+        <v>1617.33</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2008.99</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1566.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C70" s="1">
         <v>74.42</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E70" s="1">
         <v>259.89</v>
@@ -2398,10 +3031,19 @@
       <c r="F70" s="1">
         <v>370.88</v>
       </c>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="1">
+        <v>918.5500000000002</v>
+      </c>
+      <c r="H70" s="1">
+        <v>929.53</v>
+      </c>
+      <c r="I70" s="1">
+        <v>131.98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C71" s="1">
         <v>759.8900000000001</v>
@@ -2415,13 +3057,22 @@
       <c r="F71" s="1">
         <v>664.97</v>
       </c>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="1">
+        <v>904.78</v>
+      </c>
+      <c r="H71" s="1">
+        <v>606.37</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D72" s="1">
         <v>130.77</v>
@@ -2432,10 +3083,19 @@
       <c r="F72" s="1">
         <v>409.99</v>
       </c>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="1">
+        <v>1010.87</v>
+      </c>
+      <c r="H72" s="1">
+        <v>809.52</v>
+      </c>
+      <c r="I72" s="1">
+        <v>281.72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1">
         <v>92.8</v>
@@ -2444,18 +3104,27 @@
         <v>41.4</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F73" s="1">
         <v>86.98999999999999</v>
       </c>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="1">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="H73" s="1">
+        <v>82.8</v>
+      </c>
+      <c r="I73" s="1">
+        <v>637.09</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D74" s="1">
         <v>-320.14</v>
@@ -2466,10 +3135,19 @@
       <c r="F74" s="1">
         <v>272.8</v>
       </c>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="1">
+        <v>573.95</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C75" s="1">
         <v>248.98</v>
@@ -2481,12 +3159,21 @@
         <v>1189.53</v>
       </c>
       <c r="F75" s="1">
-        <v>906.3500000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>906.3499999999999</v>
+      </c>
+      <c r="G75" s="1">
+        <v>769.05</v>
+      </c>
+      <c r="H75" s="1">
+        <v>404.28</v>
+      </c>
+      <c r="I75" s="1">
+        <v>804.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C76" s="1">
         <v>144.41</v>
@@ -2500,13 +3187,22 @@
       <c r="F76" s="1">
         <v>1117.86</v>
       </c>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="G76" s="1">
+        <v>749.98</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1296.18</v>
+      </c>
+      <c r="I76" s="1">
+        <v>1339.73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D77" s="1">
         <v>701.48</v>
@@ -2517,10 +3213,19 @@
       <c r="F77" s="1">
         <v>220.58</v>
       </c>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="1">
+        <v>1235.39</v>
+      </c>
+      <c r="H77" s="1">
+        <v>236.97</v>
+      </c>
+      <c r="I77" s="1">
+        <v>144.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C78" s="1">
         <v>564.3</v>
@@ -2534,10 +3239,19 @@
       <c r="F78" s="1">
         <v>175.96</v>
       </c>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="1">
+        <v>144.99</v>
+      </c>
+      <c r="H78" s="1">
+        <v>128.39</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C79" s="1">
         <v>185.18</v>
@@ -2551,10 +3265,19 @@
       <c r="F79" s="1">
         <v>800.3099999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="1">
+        <v>385.4000000000001</v>
+      </c>
+      <c r="H79" s="1">
+        <v>542.3</v>
+      </c>
+      <c r="I79" s="1">
+        <v>219.97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C80" s="1">
         <v>1157.07</v>
@@ -2568,27 +3291,45 @@
       <c r="F80" s="1">
         <v>311.18</v>
       </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80" s="1">
+        <v>158.95</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I80" s="1">
+        <v>598.29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D81" s="1">
         <v>410.31</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F81" s="1">
         <v>88.98999999999999</v>
       </c>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="1">
+        <v>211.99</v>
+      </c>
+      <c r="H81" s="1">
+        <v>841.6</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C82" s="1">
         <v>138.6</v>
@@ -2600,18 +3341,27 @@
         <v>126.98</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G82" s="1">
+        <v>559.78</v>
+      </c>
+      <c r="H82" s="1">
+        <v>563.98</v>
+      </c>
+      <c r="I82" s="1">
+        <v>279.26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C83" s="1">
         <v>357.9000000000001</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E83" s="1">
         <v>153.99</v>
@@ -2619,16 +3369,25 @@
       <c r="F83" s="1">
         <v>136.88</v>
       </c>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="1">
+        <v>369.98</v>
+      </c>
+      <c r="H83" s="1">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="I83" s="1">
+        <v>31.39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C84" s="1">
         <v>4587.28</v>
       </c>
       <c r="D84" s="1">
-        <v>4438.55</v>
+        <v>4438.549999999999</v>
       </c>
       <c r="E84" s="1">
         <v>4040.899999999999</v>
@@ -2636,10 +3395,19 @@
       <c r="F84" s="1">
         <v>3865.96</v>
       </c>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="1">
+        <v>4201.93</v>
+      </c>
+      <c r="H84" s="1">
+        <v>5851.539999999999</v>
+      </c>
+      <c r="I84" s="1">
+        <v>4898.25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C85" s="1">
         <v>460</v>
@@ -2653,10 +3421,19 @@
       <c r="F85" s="1">
         <v>607.6900000000001</v>
       </c>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="1">
+        <v>242.54</v>
+      </c>
+      <c r="H85" s="1">
+        <v>2404</v>
+      </c>
+      <c r="I85" s="1">
+        <v>1513.76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C86" s="1">
         <v>507.99</v>
@@ -2670,10 +3447,19 @@
       <c r="F86" s="1">
         <v>141.16</v>
       </c>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="1">
+        <v>748.5599999999999</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C87" s="1">
         <v>650.49</v>
@@ -2687,13 +3473,22 @@
       <c r="F87" s="1">
         <v>384.99</v>
       </c>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="1">
+        <v>629.34</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1172.92</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1">
-        <v>474.1799999999999</v>
+        <v>474.18</v>
       </c>
       <c r="D88" s="1">
         <v>1440.56</v>
@@ -2704,10 +3499,19 @@
       <c r="F88" s="1">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="1">
+        <v>91.98</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I88" s="1">
+        <v>191.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C89" s="1">
         <v>962.0700000000001</v>
@@ -2721,10 +3525,19 @@
       <c r="F89" s="1">
         <v>1395.15</v>
       </c>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="1">
+        <v>931.96</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1341.85</v>
+      </c>
+      <c r="I89" s="1">
+        <v>418.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1">
         <v>88.98999999999999</v>
@@ -2738,10 +3551,19 @@
       <c r="F90" s="1">
         <v>319.5</v>
       </c>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" s="1">
+        <v>889.38</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I90" s="1">
+        <v>630.5999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C91" s="1">
         <v>254.97</v>
@@ -2755,13 +3577,22 @@
       <c r="F91" s="1">
         <v>1029.76</v>
       </c>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="1">
+        <v>1278.64</v>
+      </c>
+      <c r="H91" s="1">
+        <v>785.4000000000001</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1843.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D92" s="1">
         <v>422.58</v>
@@ -2772,10 +3603,19 @@
       <c r="F92" s="1">
         <v>889.22</v>
       </c>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="1">
+        <v>269.79</v>
+      </c>
+      <c r="H92" s="1">
+        <v>385.8</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C93" s="1">
         <v>1158.46</v>
@@ -2789,33 +3629,51 @@
       <c r="F93" s="1">
         <v>334.65</v>
       </c>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="1">
+        <v>126.98</v>
+      </c>
+      <c r="H93" s="1">
+        <v>638.27</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1621.61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C94" s="1">
         <v>451.78</v>
       </c>
       <c r="D94" s="1">
-        <v>966.6500000000001</v>
+        <v>966.65</v>
       </c>
       <c r="E94" s="1">
-        <v>914.0999999999999</v>
+        <v>914.1000000000001</v>
       </c>
       <c r="F94" s="1">
         <v>510.97</v>
       </c>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="1">
+        <v>554.33</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1365.28</v>
+      </c>
+      <c r="I94" s="1">
+        <v>849.3200000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C95" s="1">
         <v>1159.46</v>
       </c>
       <c r="D95" s="1">
-        <v>3419.379999999999</v>
+        <v>3419.38</v>
       </c>
       <c r="E95" s="1">
         <v>660.1900000000001</v>
@@ -2823,10 +3681,19 @@
       <c r="F95" s="1">
         <v>832.86</v>
       </c>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="1">
+        <v>2157.6</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1034.9</v>
+      </c>
+      <c r="I95" s="1">
+        <v>61.02000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C96" s="1">
         <v>2220.93</v>
@@ -2840,61 +3707,97 @@
       <c r="F96" s="1">
         <v>813</v>
       </c>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="1">
+        <v>1644</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1214.7</v>
+      </c>
+      <c r="I96" s="1">
+        <v>2206.31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1">
         <v>787.4000000000001</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G97" s="1">
+        <v>1271.37</v>
+      </c>
+      <c r="H97" s="1">
+        <v>678.3399999999999</v>
+      </c>
+      <c r="I97" s="1">
+        <v>543.98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E98" s="1">
         <v>272.66</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G98" s="1">
+        <v>302.66</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I98" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D99" s="1">
         <v>467.79</v>
       </c>
       <c r="E99" s="1">
-        <v>961.91</v>
+        <v>961.9100000000001</v>
       </c>
       <c r="F99" s="1">
         <v>921.99</v>
       </c>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="1">
+        <v>805.5</v>
+      </c>
+      <c r="H99" s="1">
+        <v>676.78</v>
+      </c>
+      <c r="I99" s="1">
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C100" s="1">
         <v>182.98</v>
@@ -2908,16 +3811,25 @@
       <c r="F100" s="1">
         <v>269.79</v>
       </c>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="1">
+        <v>402.97</v>
+      </c>
+      <c r="H100" s="1">
+        <v>202.99</v>
+      </c>
+      <c r="I100" s="1">
+        <v>588.6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1">
         <v>1984.37</v>
       </c>
       <c r="D101" s="1">
-        <v>917.37</v>
+        <v>917.3700000000001</v>
       </c>
       <c r="E101" s="1">
         <v>1019.69</v>
@@ -2925,10 +3837,19 @@
       <c r="F101" s="1">
         <v>651.77</v>
       </c>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="1">
+        <v>180</v>
+      </c>
+      <c r="H101" s="1">
+        <v>477.3800000000001</v>
+      </c>
+      <c r="I101" s="1">
+        <v>255.46</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1">
         <v>239.79</v>
@@ -2937,18 +3858,27 @@
         <v>606.23</v>
       </c>
       <c r="E102" s="1">
-        <v>746.36</v>
+        <v>746.3600000000001</v>
       </c>
       <c r="F102" s="1">
         <v>398.9</v>
       </c>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="1">
+        <v>509.28</v>
+      </c>
+      <c r="H102" s="1">
+        <v>45.99</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1091.97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D103" s="1">
         <v>269.91</v>
@@ -2959,27 +3889,45 @@
       <c r="F103" s="1">
         <v>137.97</v>
       </c>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="1">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="H103" s="1">
+        <v>834.4</v>
+      </c>
+      <c r="I103" s="1">
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1">
         <v>903.97</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E104" s="1">
         <v>315.78</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G104" s="1">
+        <v>235.68</v>
+      </c>
+      <c r="H104" s="1">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="I104" s="1">
+        <v>536.99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1">
         <v>686.0700000000001</v>
@@ -2988,32 +3936,50 @@
         <v>134.99</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F105" s="1">
-        <v>600.96</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>600.9599999999999</v>
+      </c>
+      <c r="G105" s="1">
+        <v>194.89</v>
+      </c>
+      <c r="H105" s="1">
+        <v>409.99</v>
+      </c>
+      <c r="I105" s="1">
+        <v>681.95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C106" s="1">
         <v>382.31</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E106" s="1">
         <v>499.98</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G106" s="1">
+        <v>313.5</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1915.01</v>
+      </c>
+      <c r="I106" s="1">
+        <v>283.19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C107" s="1">
         <v>272.8</v>
@@ -3027,10 +3993,19 @@
       <c r="F107" s="1">
         <v>659.1500000000001</v>
       </c>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="1">
+        <v>732.6099999999999</v>
+      </c>
+      <c r="H107" s="1">
+        <v>483.98</v>
+      </c>
+      <c r="I107" s="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C108" s="1">
         <v>1909.13</v>
@@ -3044,16 +4019,25 @@
       <c r="F108" s="1">
         <v>1401.62</v>
       </c>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="1">
+        <v>522.75</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1391.57</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C109" s="1">
         <v>700</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E109" s="1">
         <v>319.91</v>
@@ -3061,13 +4045,22 @@
       <c r="F109" s="1">
         <v>767.3</v>
       </c>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="1">
+        <v>121.5</v>
+      </c>
+      <c r="H109" s="1">
+        <v>167.28</v>
+      </c>
+      <c r="I109" s="1">
+        <v>776.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D110" s="1">
         <v>353.99</v>
@@ -3078,10 +4071,19 @@
       <c r="F110" s="1">
         <v>799.1</v>
       </c>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="1">
+        <v>559.88</v>
+      </c>
+      <c r="H110" s="1">
+        <v>189.99</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C111" s="1">
         <v>628.12</v>
@@ -3095,10 +4097,19 @@
       <c r="F111" s="1">
         <v>240.98</v>
       </c>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="1">
+        <v>421.98</v>
+      </c>
+      <c r="H111" s="1">
+        <v>782.03</v>
+      </c>
+      <c r="I111" s="1">
+        <v>124.98</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C112" s="1">
         <v>929.0799999999999</v>
@@ -3112,16 +4123,25 @@
       <c r="F112" s="1">
         <v>86.98999999999999</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="1">
+        <v>366.55</v>
+      </c>
+      <c r="H112" s="1">
+        <v>865.4000000000001</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1354.51</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C113" s="1">
         <v>341.98</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E113" s="1">
         <v>347.89</v>
@@ -3129,27 +4149,45 @@
       <c r="F113" s="1">
         <v>351.1</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="1">
+        <v>519.86</v>
+      </c>
+      <c r="H113" s="1">
+        <v>165.29</v>
+      </c>
+      <c r="I113" s="1">
+        <v>709.91</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C114" s="1">
         <v>185.89</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1">
         <v>339.92</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="1">
+        <v>71.91</v>
+      </c>
+      <c r="H114" s="1">
+        <v>558</v>
+      </c>
+      <c r="I114" s="1">
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C115" s="1">
         <v>756.41</v>
@@ -3163,13 +4201,22 @@
       <c r="F115" s="1">
         <v>199.99</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H115" s="1">
+        <v>87.38</v>
+      </c>
+      <c r="I115" s="1">
+        <v>800.46</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C116" s="1">
-        <v>464.46</v>
+        <v>464.4599999999999</v>
       </c>
       <c r="D116" s="1">
         <v>223.09</v>
@@ -3180,10 +4227,19 @@
       <c r="F116" s="1">
         <v>588.5</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="1">
+        <v>537.45</v>
+      </c>
+      <c r="H116" s="1">
+        <v>479.42</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C117" s="1">
         <v>1726.48</v>
@@ -3197,10 +4253,19 @@
       <c r="F117" s="1">
         <v>2656.84</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="1">
+        <v>1556.82</v>
+      </c>
+      <c r="H117" s="1">
+        <v>1749.35</v>
+      </c>
+      <c r="I117" s="1">
+        <v>982.64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C118" s="1">
         <v>609.97</v>
@@ -3214,16 +4279,25 @@
       <c r="F118" s="1">
         <v>45.99</v>
       </c>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" s="1">
+        <v>91.98</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I118" s="1">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C119" s="1">
-        <v>928.35</v>
+        <v>928.3499999999999</v>
       </c>
       <c r="D119" s="1">
-        <v>569.72</v>
+        <v>569.7199999999999</v>
       </c>
       <c r="E119" s="1">
         <v>943.11</v>
@@ -3231,10 +4305,19 @@
       <c r="F119" s="1">
         <v>1025.02</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="1">
+        <v>953.6700000000001</v>
+      </c>
+      <c r="H119" s="1">
+        <v>393.68</v>
+      </c>
+      <c r="I119" s="1">
+        <v>279.98</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C120" s="1">
         <v>876.6799999999999</v>
@@ -3248,10 +4331,19 @@
       <c r="F120" s="1">
         <v>1232.53</v>
       </c>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="1">
+        <v>1138.69</v>
+      </c>
+      <c r="H120" s="1">
+        <v>1590.89</v>
+      </c>
+      <c r="I120" s="1">
+        <v>635.79</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C121" s="1">
         <v>584.02</v>
@@ -3265,10 +4357,19 @@
       <c r="F121" s="1">
         <v>86.98999999999999</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I121" s="1">
+        <v>123.29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C122" s="1">
         <v>254.28</v>
@@ -3277,21 +4378,30 @@
         <v>240.98</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F122" s="1">
         <v>599.98</v>
       </c>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="1">
+        <v>889.27</v>
+      </c>
+      <c r="H122" s="1">
+        <v>635.08</v>
+      </c>
+      <c r="I122" s="1">
+        <v>536.8099999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C123" s="1">
         <v>1574.97</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E123" s="1">
         <v>45.99</v>
@@ -3299,27 +4409,45 @@
       <c r="F123" s="1">
         <v>556.4200000000001</v>
       </c>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="1">
+        <v>867.4699999999999</v>
+      </c>
+      <c r="H123" s="1">
+        <v>216.9</v>
+      </c>
+      <c r="I123" s="1">
+        <v>729.58</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C124" s="1">
         <v>646.23</v>
       </c>
       <c r="D124" s="1">
-        <v>379.68</v>
+        <v>379.6799999999999</v>
       </c>
       <c r="E124" s="1">
         <v>714.4299999999999</v>
       </c>
       <c r="F124" s="1">
-        <v>666.8700000000001</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>666.87</v>
+      </c>
+      <c r="G124" s="1">
+        <v>1134.26</v>
+      </c>
+      <c r="H124" s="1">
+        <v>1860.43</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1461.39</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1">
         <v>409.52</v>
@@ -3333,10 +4461,19 @@
       <c r="F125" s="1">
         <v>642.9400000000001</v>
       </c>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" s="1">
+        <v>339.46</v>
+      </c>
+      <c r="H125" s="1">
+        <v>132.48</v>
+      </c>
+      <c r="I125" s="1">
+        <v>536.49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C126" s="1">
         <v>508.98</v>
@@ -3348,12 +4485,21 @@
         <v>573.1500000000001</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G126" s="1">
+        <v>771.97</v>
+      </c>
+      <c r="H126" s="1">
+        <v>1214.26</v>
+      </c>
+      <c r="I126" s="1">
+        <v>718.4100000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C127" s="1">
         <v>931.1700000000001</v>
@@ -3365,12 +4511,21 @@
         <v>153.99</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G127" s="1">
+        <v>2365.81</v>
+      </c>
+      <c r="H127" s="1">
+        <v>500.97</v>
+      </c>
+      <c r="I127" s="1">
+        <v>798.0700000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C128" s="1">
         <v>245.97</v>
@@ -3382,35 +4537,53 @@
         <v>1551.82</v>
       </c>
       <c r="F128" s="1">
-        <v>583.7800000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>583.78</v>
+      </c>
+      <c r="G128" s="1">
+        <v>1474.25</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1357.27</v>
+      </c>
+      <c r="I128" s="1">
+        <v>2098.75</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D129" s="1">
         <v>407.55</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G129" s="1">
+        <v>406.98</v>
+      </c>
+      <c r="H129" s="1">
+        <v>153.99</v>
+      </c>
+      <c r="I129" s="1">
+        <v>269.99</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C130" s="1">
         <v>78.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E130" s="1">
         <v>86.98999999999999</v>
@@ -3418,10 +4591,19 @@
       <c r="F130" s="1">
         <v>63.99</v>
       </c>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H130" s="1">
+        <v>616.9000000000001</v>
+      </c>
+      <c r="I130" s="1">
+        <v>86.98999999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C131" s="1">
         <v>385.43</v>
@@ -3430,15 +4612,24 @@
         <v>824.73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G131" s="1">
+        <v>937.3200000000001</v>
+      </c>
+      <c r="H131" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="I131" s="1">
+        <v>759.2600000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1">
         <v>1034.53</v>
@@ -3447,32 +4638,50 @@
         <v>1089.39</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F132" s="1">
-        <v>878.4200000000001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>878.42</v>
+      </c>
+      <c r="G132" s="1">
+        <v>1364.3</v>
+      </c>
+      <c r="H132" s="1">
+        <v>496.6</v>
+      </c>
+      <c r="I132" s="1">
+        <v>462.56</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C133" s="1">
         <v>809.48</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G133" s="1">
+        <v>370.98</v>
+      </c>
+      <c r="H133" s="1">
+        <v>384.99</v>
+      </c>
+      <c r="I133" s="1">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C134" s="1">
         <v>45.99</v>
@@ -3486,10 +4695,19 @@
       <c r="F134" s="1">
         <v>375.47</v>
       </c>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H134" s="1">
+        <v>1041.64</v>
+      </c>
+      <c r="I134" s="1">
+        <v>83.99000000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C135" s="1">
         <v>495.38</v>
@@ -3501,12 +4719,21 @@
         <v>153.99</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G135" s="1">
+        <v>535.97</v>
+      </c>
+      <c r="H135" s="1">
+        <v>557.1700000000001</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C136" s="1">
         <v>1098.08</v>
@@ -3520,10 +4747,19 @@
       <c r="F136" s="1">
         <v>1651.32</v>
       </c>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="1">
+        <v>848.45</v>
+      </c>
+      <c r="H136" s="1">
+        <v>1176.91</v>
+      </c>
+      <c r="I136" s="1">
+        <v>449.99</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C137" s="1">
         <v>399.84</v>
@@ -3532,15 +4768,24 @@
         <v>90.98</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F137" s="1">
         <v>136.46</v>
       </c>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="1">
+        <v>1616.59</v>
+      </c>
+      <c r="H137" s="1">
+        <v>749.98</v>
+      </c>
+      <c r="I137" s="1">
+        <v>421.72</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C138" s="1">
         <v>1087.58</v>
@@ -3554,10 +4799,19 @@
       <c r="F138" s="1">
         <v>2257.65</v>
       </c>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="1">
+        <v>253.98</v>
+      </c>
+      <c r="H138" s="1">
+        <v>957.6700000000001</v>
+      </c>
+      <c r="I138" s="1">
+        <v>656.96</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C139" s="1">
         <v>525.4100000000001</v>
@@ -3571,16 +4825,25 @@
       <c r="F139" s="1">
         <v>280.15</v>
       </c>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" s="1">
+        <v>512.95</v>
+      </c>
+      <c r="H139" s="1">
+        <v>1399.74</v>
+      </c>
+      <c r="I139" s="1">
+        <v>2230.96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C140" s="1">
         <v>78.29000000000001</v>
       </c>
       <c r="D140" s="1">
-        <v>640.8699999999999</v>
+        <v>640.87</v>
       </c>
       <c r="E140" s="1">
         <v>298.46</v>
@@ -3588,10 +4851,19 @@
       <c r="F140" s="1">
         <v>486.9000000000001</v>
       </c>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" s="1">
+        <v>88.30000000000001</v>
+      </c>
+      <c r="H140" s="1">
+        <v>353.44</v>
+      </c>
+      <c r="I140" s="1">
+        <v>505.17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C141" s="1">
         <v>782.86</v>
@@ -3605,10 +4877,19 @@
       <c r="F141" s="1">
         <v>398.16</v>
       </c>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" s="1">
+        <v>336.99</v>
+      </c>
+      <c r="H141" s="1">
+        <v>954.87</v>
+      </c>
+      <c r="I141" s="1">
+        <v>512.4400000000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C142" s="1">
         <v>570.6</v>
@@ -3617,18 +4898,27 @@
         <v>202.99</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F142" s="1">
         <v>124.19</v>
       </c>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="1">
+        <v>478.98</v>
+      </c>
+      <c r="H142" s="1">
+        <v>476.57</v>
+      </c>
+      <c r="I142" s="1">
+        <v>384.9000000000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C143" s="1">
-        <v>645.12</v>
+        <v>645.1199999999999</v>
       </c>
       <c r="D143" s="1">
         <v>468.38</v>
@@ -3639,10 +4929,19 @@
       <c r="F143" s="1">
         <v>634.88</v>
       </c>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="1">
+        <v>1658.89</v>
+      </c>
+      <c r="H143" s="1">
+        <v>1077.04</v>
+      </c>
+      <c r="I143" s="1">
+        <v>754.25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C144" s="1">
         <v>769.88</v>
@@ -3651,15 +4950,24 @@
         <v>248.98</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I144" s="1">
+        <v>403.65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C145" s="1">
         <v>357.49</v>
@@ -3673,27 +4981,45 @@
       <c r="F145" s="1">
         <v>124.99</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="1">
+        <v>124.99</v>
+      </c>
+      <c r="H145" s="1">
+        <v>1169.88</v>
+      </c>
+      <c r="I145" s="1">
+        <v>719.98</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D146" s="1">
         <v>132.98</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F146" s="1">
         <v>45.43</v>
       </c>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="1">
+        <v>571.85</v>
+      </c>
+      <c r="H146" s="1">
+        <v>228.98</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C147" s="1">
         <v>338.38</v>
@@ -3707,13 +5033,22 @@
       <c r="F147" s="1">
         <v>717</v>
       </c>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" s="1">
+        <v>491.33</v>
+      </c>
+      <c r="H147" s="1">
+        <v>138.59</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C148" s="1">
-        <v>2745.440000000001</v>
+        <v>2745.44</v>
       </c>
       <c r="D148" s="1">
         <v>194.62</v>
@@ -3724,27 +5059,45 @@
       <c r="F148" s="1">
         <v>1177.52</v>
       </c>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="1">
+        <v>2071.18</v>
+      </c>
+      <c r="H148" s="1">
+        <v>1507.61</v>
+      </c>
+      <c r="I148" s="1">
+        <v>2059.45</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C149" s="1">
         <v>199.99</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E149" s="1">
         <v>334.79</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H149" s="1">
+        <v>635.9</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C150" s="1">
         <v>818.5</v>
@@ -3758,10 +5111,19 @@
       <c r="F150" s="1">
         <v>264.78</v>
       </c>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="1">
+        <v>1269.29</v>
+      </c>
+      <c r="H150" s="1">
+        <v>1214.69</v>
+      </c>
+      <c r="I150" s="1">
+        <v>712.3900000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C151" s="1">
         <v>707.01</v>
@@ -3775,10 +5137,19 @@
       <c r="F151" s="1">
         <v>367.38</v>
       </c>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" s="1">
+        <v>587.3800000000001</v>
+      </c>
+      <c r="H151" s="1">
+        <v>548.28</v>
+      </c>
+      <c r="I151" s="1">
+        <v>1325.76</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C152" s="1">
         <v>155.28</v>
@@ -3792,10 +5163,19 @@
       <c r="F152" s="1">
         <v>448.29</v>
       </c>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="G152" s="1">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H152" s="1">
+        <v>496.77</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C153" s="1">
         <v>1235.5</v>
@@ -3809,10 +5189,19 @@
       <c r="F153" s="1">
         <v>1340.36</v>
       </c>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="1">
+        <v>1357.97</v>
+      </c>
+      <c r="H153" s="1">
+        <v>784.85</v>
+      </c>
+      <c r="I153" s="1">
+        <v>583.49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C154" s="1">
         <v>1346.48</v>
@@ -3826,10 +5215,19 @@
       <c r="F154" s="1">
         <v>1608.46</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="1">
+        <v>1194.84</v>
+      </c>
+      <c r="H154" s="1">
+        <v>1915.46</v>
+      </c>
+      <c r="I154" s="1">
+        <v>853.9400000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C155" s="1">
         <v>1384</v>
@@ -3843,10 +5241,19 @@
       <c r="F155" s="1">
         <v>1079.01</v>
       </c>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" s="1">
+        <v>1224.69</v>
+      </c>
+      <c r="H155" s="1">
+        <v>1844.7</v>
+      </c>
+      <c r="I155" s="1">
+        <v>981.29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C156" s="1">
         <v>144.49</v>
@@ -3860,10 +5267,19 @@
       <c r="F156" s="1">
         <v>838.4100000000001</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="1">
+        <v>691.47</v>
+      </c>
+      <c r="H156" s="1">
+        <v>145.09</v>
+      </c>
+      <c r="I156" s="1">
+        <v>1346.98</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C157" s="1">
         <v>492.52</v>
@@ -3877,10 +5293,19 @@
       <c r="F157" s="1">
         <v>849.15</v>
       </c>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" s="1">
+        <v>1266.72</v>
+      </c>
+      <c r="H157" s="1">
+        <v>459.97</v>
+      </c>
+      <c r="I157" s="1">
+        <v>320.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C158" s="1">
         <v>1288.35</v>
@@ -3894,10 +5319,19 @@
       <c r="F158" s="1">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" s="1">
+        <v>810.0899999999999</v>
+      </c>
+      <c r="H158" s="1">
+        <v>250.73</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C159" s="1">
         <v>217.11</v>
@@ -3911,10 +5345,19 @@
       <c r="F159" s="1">
         <v>351.96</v>
       </c>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" s="1">
+        <v>2060.17</v>
+      </c>
+      <c r="H159" s="1">
+        <v>879.3</v>
+      </c>
+      <c r="I159" s="1">
+        <v>1317.66</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C160" s="1">
         <v>1190.43</v>
@@ -3928,13 +5371,22 @@
       <c r="F160" s="1">
         <v>567.9</v>
       </c>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="1">
+        <v>1665.53</v>
+      </c>
+      <c r="H160" s="1">
+        <v>237.44</v>
+      </c>
+      <c r="I160" s="1">
+        <v>153.99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D161" s="1">
         <v>314.99</v>
@@ -3945,10 +5397,19 @@
       <c r="F161" s="1">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="G161" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I161" s="1">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C162" s="1">
         <v>1130.93</v>
@@ -3962,10 +5423,19 @@
       <c r="F162" s="1">
         <v>278.97</v>
       </c>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="1">
+        <v>398.22</v>
+      </c>
+      <c r="H162" s="1">
+        <v>1172.13</v>
+      </c>
+      <c r="I162" s="1">
+        <v>547.05</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C163" s="1">
         <v>86.98999999999999</v>
@@ -3979,10 +5449,19 @@
       <c r="F163" s="1">
         <v>244.17</v>
       </c>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="1">
+        <v>581.79</v>
+      </c>
+      <c r="H163" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="I163" s="1">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C164" s="1">
         <v>637.22</v>
@@ -3996,10 +5475,19 @@
       <c r="F164" s="1">
         <v>914.47</v>
       </c>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" s="1">
+        <v>1252.98</v>
+      </c>
+      <c r="H164" s="1">
+        <v>796.3600000000001</v>
+      </c>
+      <c r="I164" s="1">
+        <v>401.87</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C165" s="1">
         <v>604.49</v>
@@ -4013,10 +5501,19 @@
       <c r="F165" s="1">
         <v>708.78</v>
       </c>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H165" s="1">
+        <v>438.26</v>
+      </c>
+      <c r="I165" s="1">
+        <v>737.5700000000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C166" s="1">
         <v>2220.32</v>
@@ -4030,13 +5527,22 @@
       <c r="F166" s="1">
         <v>1737.41</v>
       </c>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="1">
+        <v>51.49000000000001</v>
+      </c>
+      <c r="H166" s="1">
+        <v>1718.63</v>
+      </c>
+      <c r="I166" s="1">
+        <v>3569.439999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D167" s="1">
         <v>445.95</v>
@@ -4045,12 +5551,21 @@
         <v>275.99</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H167" s="1">
+        <v>347.19</v>
+      </c>
+      <c r="I167" s="1">
+        <v>80.98999999999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C168" s="1">
         <v>1226.37</v>
@@ -4064,10 +5579,19 @@
       <c r="F168" s="1">
         <v>533.02</v>
       </c>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="1">
+        <v>1576.55</v>
+      </c>
+      <c r="H168" s="1">
+        <v>2166.8</v>
+      </c>
+      <c r="I168" s="1">
+        <v>952.97</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C169" s="1">
         <v>452.29</v>
@@ -4079,12 +5603,21 @@
         <v>741.97</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G169" s="1">
+        <v>566.3199999999999</v>
+      </c>
+      <c r="H169" s="1">
+        <v>313.2</v>
+      </c>
+      <c r="I169" s="1">
+        <v>206.99</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C170" s="1">
         <v>447.1</v>
@@ -4098,10 +5631,19 @@
       <c r="F170" s="1">
         <v>529.83</v>
       </c>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="1">
+        <v>907.0700000000001</v>
+      </c>
+      <c r="H170" s="1">
+        <v>223.68</v>
+      </c>
+      <c r="I170" s="1">
+        <v>470.82</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C171" s="1">
         <v>1365.74</v>
@@ -4115,10 +5657,19 @@
       <c r="F171" s="1">
         <v>303.3</v>
       </c>
-    </row>
-    <row r="172" spans="1:6">
+      <c r="G171" s="1">
+        <v>895.4400000000001</v>
+      </c>
+      <c r="H171" s="1">
+        <v>701.55</v>
+      </c>
+      <c r="I171" s="1">
+        <v>1905.1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C172" s="1">
         <v>1435.79</v>
@@ -4132,10 +5683,19 @@
       <c r="F172" s="1">
         <v>1305.54</v>
       </c>
-    </row>
-    <row r="173" spans="1:6">
+      <c r="G172" s="1">
+        <v>2275.77</v>
+      </c>
+      <c r="H172" s="1">
+        <v>799.22</v>
+      </c>
+      <c r="I172" s="1">
+        <v>964.3099999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C173" s="1">
         <v>579.98</v>
@@ -4149,10 +5709,19 @@
       <c r="F173" s="1">
         <v>124.98</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="1">
+        <v>731.97</v>
+      </c>
+      <c r="H173" s="1">
+        <v>933.95</v>
+      </c>
+      <c r="I173" s="1">
+        <v>1307.64</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C174" s="1">
         <v>542.51</v>
@@ -4166,10 +5735,19 @@
       <c r="F174" s="1">
         <v>47.94</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="1">
+        <v>602.98</v>
+      </c>
+      <c r="H174" s="1">
+        <v>1794.76</v>
+      </c>
+      <c r="I174" s="1">
+        <v>604.15</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C175" s="1">
         <v>78.3</v>
@@ -4183,13 +5761,22 @@
       <c r="F175" s="1">
         <v>365.98</v>
       </c>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="1">
+        <v>478.48</v>
+      </c>
+      <c r="H175" s="1">
+        <v>311.69</v>
+      </c>
+      <c r="I175" s="1">
+        <v>528.62</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D176" s="1">
         <v>380.31</v>
@@ -4200,10 +5787,19 @@
       <c r="F176" s="1">
         <v>79.98999999999999</v>
       </c>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I176" s="1">
+        <v>324.99</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C177" s="1">
         <v>907.1900000000001</v>
@@ -4217,13 +5813,22 @@
       <c r="F177" s="1">
         <v>521.89</v>
       </c>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="1">
+        <v>248.5</v>
+      </c>
+      <c r="H177" s="1">
+        <v>948.26</v>
+      </c>
+      <c r="I177" s="1">
+        <v>583.98</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D178" s="1">
         <v>409.99</v>
@@ -4234,10 +5839,19 @@
       <c r="F178" s="1">
         <v>399.99</v>
       </c>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I178" s="1">
+        <v>91.98</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C179" s="1">
         <v>445.97</v>
@@ -4249,12 +5863,21 @@
         <v>140</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G179" s="1">
+        <v>138.6</v>
+      </c>
+      <c r="H179" s="1">
+        <v>334.18</v>
+      </c>
+      <c r="I179" s="1">
+        <v>803.72</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C180" s="1">
         <v>450</v>
@@ -4268,10 +5891,19 @@
       <c r="F180" s="1">
         <v>44.99</v>
       </c>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="1">
+        <v>324.48</v>
+      </c>
+      <c r="H180" s="1">
+        <v>690.38</v>
+      </c>
+      <c r="I180" s="1">
+        <v>250.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C181" s="1">
         <v>377.82</v>
@@ -4285,10 +5917,19 @@
       <c r="F181" s="1">
         <v>158.29</v>
       </c>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I181" s="1">
+        <v>339.99</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C182" s="1">
         <v>414.31</v>
@@ -4300,15 +5941,24 @@
         <v>720.4400000000001</v>
       </c>
       <c r="F182" s="1">
-        <v>532.72</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
+        <v>532.7199999999999</v>
+      </c>
+      <c r="G182" s="1">
+        <v>417.87</v>
+      </c>
+      <c r="H182" s="1">
+        <v>266.82</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C183" s="1">
-        <v>834.36</v>
+        <v>834.3600000000001</v>
       </c>
       <c r="D183" s="1">
         <v>847.48</v>
@@ -4319,10 +5969,19 @@
       <c r="F183" s="1">
         <v>696.96</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="1">
+        <v>367.26</v>
+      </c>
+      <c r="H183" s="1">
+        <v>1206.08</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C184" s="1">
         <v>1934.34</v>
@@ -4336,10 +5995,19 @@
       <c r="F184" s="1">
         <v>1571.96</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="1">
+        <v>765.5700000000001</v>
+      </c>
+      <c r="H184" s="1">
+        <v>1703.69</v>
+      </c>
+      <c r="I184" s="1">
+        <v>877.01</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C185" s="1">
         <v>1449.5</v>
@@ -4353,10 +6021,19 @@
       <c r="F185" s="1">
         <v>463.21</v>
       </c>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="G185" s="1">
+        <v>259.99</v>
+      </c>
+      <c r="H185" s="1">
+        <v>658.95</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C186" s="1">
         <v>1576.84</v>
@@ -4370,10 +6047,19 @@
       <c r="F186" s="1">
         <v>671.3099999999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="1">
+        <v>161.89</v>
+      </c>
+      <c r="H186" s="1">
+        <v>247.98</v>
+      </c>
+      <c r="I186" s="1">
+        <v>657.5700000000001</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C187" s="1">
         <v>1513.35</v>
@@ -4385,12 +6071,21 @@
         <v>922.0200000000001</v>
       </c>
       <c r="F187" s="1">
-        <v>3788.399999999999</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
+        <v>3788.4</v>
+      </c>
+      <c r="G187" s="1">
+        <v>2878</v>
+      </c>
+      <c r="H187" s="1">
+        <v>1316.74</v>
+      </c>
+      <c r="I187" s="1">
+        <v>1831.21</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C188" s="1">
         <v>198.89</v>
@@ -4404,10 +6099,19 @@
       <c r="F188" s="1">
         <v>1422.4</v>
       </c>
-    </row>
-    <row r="189" spans="1:6">
+      <c r="G188" s="1">
+        <v>1073.46</v>
+      </c>
+      <c r="H188" s="1">
+        <v>1091.81</v>
+      </c>
+      <c r="I188" s="1">
+        <v>655.6900000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C189" s="1">
         <v>409.99</v>
@@ -4421,16 +6125,25 @@
       <c r="F189" s="1">
         <v>1744.46</v>
       </c>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="1">
+        <v>1057.93</v>
+      </c>
+      <c r="H189" s="1">
+        <v>1549.3</v>
+      </c>
+      <c r="I189" s="1">
+        <v>124.99</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C190" s="1">
         <v>72.90000000000001</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E190" s="1">
         <v>45.99</v>
@@ -4438,10 +6151,19 @@
       <c r="F190" s="1">
         <v>367.97</v>
       </c>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="1">
+        <v>179.87</v>
+      </c>
+      <c r="H190" s="1">
+        <v>483.21</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C191" s="1">
         <v>1442.66</v>
@@ -4455,10 +6177,19 @@
       <c r="F191" s="1">
         <v>80.09999999999999</v>
       </c>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="1">
+        <v>662.28</v>
+      </c>
+      <c r="H191" s="1">
+        <v>552.51</v>
+      </c>
+      <c r="I191" s="1">
+        <v>573.51</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C192" s="1">
         <v>1167.7</v>
@@ -4472,10 +6203,19 @@
       <c r="F192" s="1">
         <v>1470.6</v>
       </c>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="1">
+        <v>784.7099999999999</v>
+      </c>
+      <c r="H192" s="1">
+        <v>924.1900000000001</v>
+      </c>
+      <c r="I192" s="1">
+        <v>1374.74</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C193" s="1">
         <v>783.09</v>
@@ -4489,16 +6229,25 @@
       <c r="F193" s="1">
         <v>1369.7</v>
       </c>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="G193" s="1">
+        <v>1227.2</v>
+      </c>
+      <c r="H193" s="1">
+        <v>1975.84</v>
+      </c>
+      <c r="I193" s="1">
+        <v>881.5700000000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C194" s="1">
         <v>942.99</v>
       </c>
       <c r="D194" s="1">
-        <v>912.3000000000002</v>
+        <v>912.3</v>
       </c>
       <c r="E194" s="1">
         <v>491.52</v>
@@ -4506,10 +6255,19 @@
       <c r="F194" s="1">
         <v>1892.16</v>
       </c>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="1">
+        <v>752.99</v>
+      </c>
+      <c r="H194" s="1">
+        <v>593.46</v>
+      </c>
+      <c r="I194" s="1">
+        <v>912.0800000000002</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C195" s="1">
         <v>227.59</v>
@@ -4523,10 +6281,19 @@
       <c r="F195" s="1">
         <v>131.58</v>
       </c>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="1">
+        <v>131.58</v>
+      </c>
+      <c r="H195" s="1">
+        <v>538.02</v>
+      </c>
+      <c r="I195" s="1">
+        <v>202.99</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C196" s="1">
         <v>1856.06</v>
@@ -4540,10 +6307,19 @@
       <c r="F196" s="1">
         <v>307.98</v>
       </c>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" s="1">
+        <v>1642.47</v>
+      </c>
+      <c r="H196" s="1">
+        <v>1144.35</v>
+      </c>
+      <c r="I196" s="1">
+        <v>209.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C197" s="1">
         <v>1430.69</v>
@@ -4557,10 +6333,19 @@
       <c r="F197" s="1">
         <v>344.51</v>
       </c>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="1">
+        <v>499.2</v>
+      </c>
+      <c r="H197" s="1">
+        <v>823.1900000000001</v>
+      </c>
+      <c r="I197" s="1">
+        <v>1400.1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C198" s="1">
         <v>190.8</v>
@@ -4574,10 +6359,19 @@
       <c r="F198" s="1">
         <v>241.67</v>
       </c>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="1">
+        <v>123.3</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I198" s="1">
+        <v>573.78</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C199" s="1">
         <v>88.98999999999999</v>
@@ -4591,27 +6385,45 @@
       <c r="F199" s="1">
         <v>579.79</v>
       </c>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="1">
+        <v>420.91</v>
+      </c>
+      <c r="H199" s="1">
+        <v>971.72</v>
+      </c>
+      <c r="I199" s="1">
+        <v>249.29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C200" s="1">
         <v>1333.5</v>
       </c>
       <c r="D200" s="1">
-        <v>763.05</v>
+        <v>763.0500000000002</v>
       </c>
       <c r="E200" s="1">
         <v>3168.45</v>
       </c>
       <c r="F200" s="1">
-        <v>928.7100000000002</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
+        <v>928.71</v>
+      </c>
+      <c r="G200" s="1">
+        <v>1769.03</v>
+      </c>
+      <c r="H200" s="1">
+        <v>2317.64</v>
+      </c>
+      <c r="I200" s="1">
+        <v>2982.15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C201" s="1">
         <v>1199.37</v>
@@ -4623,18 +6435,27 @@
         <v>1289.11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
+        <v>10</v>
+      </c>
+      <c r="G201" s="1">
+        <v>251.88</v>
+      </c>
+      <c r="H201" s="1">
+        <v>1198.5</v>
+      </c>
+      <c r="I201" s="1">
+        <v>309.01</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C202" s="1">
         <v>86.98999999999999</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E202" s="1">
         <v>434.97</v>
@@ -4642,1114 +6463,1734 @@
       <c r="F202" s="1">
         <v>671.62</v>
       </c>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="G202" s="1">
+        <v>542.8</v>
+      </c>
+      <c r="H202" s="1">
+        <v>333.79</v>
+      </c>
+      <c r="I202" s="1">
+        <v>40.49</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>208</v>
-      </c>
-      <c r="C203" s="1">
+        <v>211</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H203" s="1">
+        <v>277.96</v>
+      </c>
+      <c r="I203" s="1">
+        <v>138.6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>212</v>
+      </c>
+      <c r="C204" s="1">
         <v>78.3</v>
       </c>
-      <c r="D203" s="1">
+      <c r="D204" s="1">
         <v>436.81</v>
       </c>
-      <c r="E203" s="1">
-        <v>886.6999999999998</v>
-      </c>
-      <c r="F203" s="1">
+      <c r="E204" s="1">
+        <v>886.7</v>
+      </c>
+      <c r="F204" s="1">
         <v>600.38</v>
       </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204" t="s">
-        <v>209</v>
-      </c>
-      <c r="C204" s="1">
+      <c r="G204" s="1">
+        <v>570.88</v>
+      </c>
+      <c r="H204" s="1">
+        <v>838.29</v>
+      </c>
+      <c r="I204" s="1">
+        <v>763.36</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" s="1">
         <v>376.18</v>
       </c>
-      <c r="D204" s="1">
+      <c r="D205" s="1">
         <v>794.5700000000001</v>
       </c>
-      <c r="E204" s="1">
+      <c r="E205" s="1">
         <v>341.91</v>
       </c>
-      <c r="F204" s="1">
+      <c r="F205" s="1">
         <v>1577.19</v>
       </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205" t="s">
-        <v>210</v>
-      </c>
-      <c r="C205" s="1">
+      <c r="G205" s="1">
+        <v>302.66</v>
+      </c>
+      <c r="H205" s="1">
+        <v>320.4</v>
+      </c>
+      <c r="I205" s="1">
+        <v>587.39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" s="1">
         <v>324.99</v>
       </c>
-      <c r="D205" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E205" s="1">
+      <c r="D206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206" s="1">
         <v>838.28</v>
       </c>
-      <c r="F205" s="1">
+      <c r="F206" s="1">
         <v>602.98</v>
       </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206" t="s">
-        <v>211</v>
-      </c>
-      <c r="C206" s="1">
+      <c r="G206" s="1">
+        <v>410.98</v>
+      </c>
+      <c r="H206" s="1">
+        <v>240.28</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>215</v>
+      </c>
+      <c r="C207" s="1">
         <v>123.29</v>
       </c>
-      <c r="D206" s="1">
+      <c r="D207" s="1">
         <v>440.79</v>
       </c>
-      <c r="E206" s="1">
+      <c r="E207" s="1">
         <v>40.5</v>
       </c>
-      <c r="F206" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207" t="s">
-        <v>212</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E207" s="1">
+      <c r="F207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="1">
+        <v>886.97</v>
+      </c>
+      <c r="H207" s="1">
+        <v>319.5</v>
+      </c>
+      <c r="I207" s="1">
+        <v>535.8499999999999</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>216</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E208" s="1">
         <v>32.39</v>
       </c>
-      <c r="F207" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208" t="s">
-        <v>213</v>
-      </c>
-      <c r="C208" s="1">
+      <c r="F208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="1">
+        <v>358.88</v>
+      </c>
+      <c r="H208" s="1">
+        <v>124.99</v>
+      </c>
+      <c r="I208" s="1">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>217</v>
+      </c>
+      <c r="C209" s="1">
         <v>317.6500000000001</v>
       </c>
-      <c r="D208" s="1">
+      <c r="D209" s="1">
         <v>78.29000000000001</v>
       </c>
-      <c r="E208" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209" t="s">
-        <v>214</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D209" s="1">
+      <c r="E209" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="1">
+        <v>506.96</v>
+      </c>
+      <c r="H209" s="1">
+        <v>173.98</v>
+      </c>
+      <c r="I209" s="1">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>218</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D210" s="1">
         <v>561.12</v>
       </c>
-      <c r="E209" s="1">
+      <c r="E210" s="1">
         <v>340.64</v>
       </c>
-      <c r="F209" s="1">
+      <c r="F210" s="1">
         <v>632.11</v>
       </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210" t="s">
-        <v>215</v>
-      </c>
-      <c r="C210" s="1">
+      <c r="G210" s="1">
+        <v>45.99</v>
+      </c>
+      <c r="H210" s="1">
+        <v>399.99</v>
+      </c>
+      <c r="I210" s="1">
+        <v>626.6700000000001</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>219</v>
+      </c>
+      <c r="C211" s="1">
         <v>1094.13</v>
       </c>
-      <c r="D210" s="1">
+      <c r="D211" s="1">
         <v>533.97</v>
       </c>
-      <c r="E210" s="1">
-        <v>721.59</v>
-      </c>
-      <c r="F210" s="1">
+      <c r="E211" s="1">
+        <v>721.5899999999999</v>
+      </c>
+      <c r="F211" s="1">
         <v>659.49</v>
       </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211" t="s">
-        <v>216</v>
-      </c>
-      <c r="C211" s="1">
+      <c r="G211" s="1">
+        <v>173.38</v>
+      </c>
+      <c r="H211" s="1">
+        <v>1686.56</v>
+      </c>
+      <c r="I211" s="1">
+        <v>1992.91</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>220</v>
+      </c>
+      <c r="C212" s="1">
         <v>37.4</v>
       </c>
-      <c r="D211" s="1">
+      <c r="D212" s="1">
         <v>86.98999999999999</v>
       </c>
-      <c r="E211" s="1">
+      <c r="E212" s="1">
         <v>341.91</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F212" s="1">
         <v>324.99</v>
       </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212" t="s">
-        <v>217</v>
-      </c>
-      <c r="C212" s="1">
+      <c r="G212" s="1">
+        <v>315.99</v>
+      </c>
+      <c r="H212" s="1">
+        <v>359.91</v>
+      </c>
+      <c r="I212" s="1">
+        <v>131.98</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>221</v>
+      </c>
+      <c r="C213" s="1">
         <v>1263.72</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F212" s="1">
+      <c r="D213" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F213" s="1">
         <v>39.24</v>
       </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213" t="s">
-        <v>218</v>
-      </c>
-      <c r="C213" s="1">
+      <c r="G213" s="1">
+        <v>296.98</v>
+      </c>
+      <c r="H213" s="1">
+        <v>350.28</v>
+      </c>
+      <c r="I213" s="1">
+        <v>63.99</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>222</v>
+      </c>
+      <c r="C214" s="1">
         <v>118.89</v>
       </c>
-      <c r="D213" s="1">
+      <c r="D214" s="1">
         <v>444.9</v>
       </c>
-      <c r="E213" s="1">
+      <c r="E214" s="1">
         <v>289.99</v>
       </c>
-      <c r="F213" s="1">
+      <c r="F214" s="1">
         <v>226.22</v>
       </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214" t="s">
-        <v>219</v>
-      </c>
-      <c r="C214" s="1">
+      <c r="G214" s="1">
+        <v>593.87</v>
+      </c>
+      <c r="H214" s="1">
+        <v>634.98</v>
+      </c>
+      <c r="I214" s="1">
+        <v>1210.56</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>223</v>
+      </c>
+      <c r="C215" s="1">
         <v>170.5</v>
       </c>
-      <c r="D214" s="1">
+      <c r="D215" s="1">
         <v>86.98999999999999</v>
       </c>
-      <c r="E214" s="1">
+      <c r="E215" s="1">
         <v>1009.79</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F215" s="1">
         <v>369.06</v>
       </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215" t="s">
-        <v>220</v>
-      </c>
-      <c r="C215" s="1">
+      <c r="G215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I215" s="1">
+        <v>357.16</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>224</v>
+      </c>
+      <c r="C216" s="1">
         <v>179.99</v>
       </c>
-      <c r="D215" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F215" s="1">
+      <c r="D216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" s="1">
         <v>170.98</v>
       </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216" t="s">
-        <v>221</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D216" s="1">
+      <c r="G216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H216" s="1">
+        <v>105.39</v>
+      </c>
+      <c r="I216" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>225</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="1">
         <v>623.5599999999999</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E217" s="1">
         <v>324.49</v>
       </c>
-      <c r="F216" s="1">
+      <c r="F217" s="1">
         <v>181.99</v>
       </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217" t="s">
-        <v>222</v>
-      </c>
-      <c r="C217" s="1">
+      <c r="G217" s="1">
+        <v>247.8</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I217" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>226</v>
+      </c>
+      <c r="C218" s="1">
         <v>78.3</v>
       </c>
-      <c r="D217" s="1">
+      <c r="D218" s="1">
         <v>578.98</v>
       </c>
-      <c r="E217" s="1">
+      <c r="E218" s="1">
         <v>41.4</v>
       </c>
-      <c r="F217" s="1">
+      <c r="F218" s="1">
         <v>565.53</v>
       </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218" t="s">
-        <v>223</v>
-      </c>
-      <c r="C218" s="1">
+      <c r="G218" s="1">
+        <v>248.49</v>
+      </c>
+      <c r="H218" s="1">
+        <v>319.99</v>
+      </c>
+      <c r="I218" s="1">
+        <v>495.79</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>227</v>
+      </c>
+      <c r="C219" s="1">
         <v>153.99</v>
       </c>
-      <c r="D218" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E218" s="1">
+      <c r="D219" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E219" s="1">
         <v>70.98999999999999</v>
       </c>
-      <c r="F218" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219" t="s">
-        <v>224</v>
-      </c>
-      <c r="C219" s="1">
+      <c r="F219" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="1">
+        <v>92.89</v>
+      </c>
+      <c r="H219" s="1">
+        <v>700.2</v>
+      </c>
+      <c r="I219" s="1">
+        <v>327.98</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>228</v>
+      </c>
+      <c r="C220" s="1">
         <v>45.99</v>
       </c>
-      <c r="D219" s="1">
+      <c r="D220" s="1">
         <v>1202.88</v>
       </c>
-      <c r="E219" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F219" s="1">
+      <c r="E220" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F220" s="1">
         <v>254</v>
       </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220" t="s">
-        <v>225</v>
-      </c>
-      <c r="C220" s="1">
+      <c r="G220" s="1">
+        <v>450</v>
+      </c>
+      <c r="H220" s="1">
+        <v>306.17</v>
+      </c>
+      <c r="I220" s="1">
+        <v>394.91</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>229</v>
+      </c>
+      <c r="C221" s="1">
         <v>1351.11</v>
       </c>
-      <c r="D220" s="1">
+      <c r="D221" s="1">
         <v>901.26</v>
       </c>
-      <c r="E220" s="1">
+      <c r="E221" s="1">
         <v>241.39</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F221" s="1">
         <v>487.27</v>
       </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221" t="s">
-        <v>226</v>
-      </c>
-      <c r="C221" s="1">
+      <c r="G221" s="1">
+        <v>1303.27</v>
+      </c>
+      <c r="H221" s="1">
+        <v>961.76</v>
+      </c>
+      <c r="I221" s="1">
+        <v>1062.63</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>230</v>
+      </c>
+      <c r="C222" s="1">
         <v>182.7</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E221" s="1">
+      <c r="D222" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E222" s="1">
         <v>802.6900000000001</v>
       </c>
-      <c r="F221" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222" t="s">
-        <v>227</v>
-      </c>
-      <c r="C222" s="1">
+      <c r="F222" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="1">
+        <v>1104.16</v>
+      </c>
+      <c r="H222" s="1">
+        <v>44.99</v>
+      </c>
+      <c r="I222" s="1">
+        <v>782.6700000000001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>231</v>
+      </c>
+      <c r="C223" s="1">
         <v>3524.67</v>
       </c>
-      <c r="D222" s="1">
+      <c r="D223" s="1">
         <v>1301.86</v>
       </c>
-      <c r="E222" s="1">
+      <c r="E223" s="1">
         <v>2583.69</v>
       </c>
-      <c r="F222" s="1">
+      <c r="F223" s="1">
         <v>894.8700000000001</v>
       </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223" t="s">
-        <v>228</v>
-      </c>
-      <c r="C223" s="1">
+      <c r="G223" s="1">
+        <v>1171.53</v>
+      </c>
+      <c r="H223" s="1">
+        <v>2345.940000000001</v>
+      </c>
+      <c r="I223" s="1">
+        <v>575.97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>232</v>
+      </c>
+      <c r="C224" s="1">
         <v>532.96</v>
       </c>
-      <c r="D223" s="1">
+      <c r="D224" s="1">
         <v>269.79</v>
       </c>
-      <c r="E223" s="1">
+      <c r="E224" s="1">
         <v>60.9</v>
       </c>
-      <c r="F223" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6">
-      <c r="A224" t="s">
-        <v>229</v>
-      </c>
-      <c r="C224" s="1">
+      <c r="F224" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="1">
+        <v>45.99</v>
+      </c>
+      <c r="H224" s="1">
+        <v>263.7</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>233</v>
+      </c>
+      <c r="C225" s="1">
         <v>649.99</v>
       </c>
-      <c r="D224" s="1">
+      <c r="D225" s="1">
         <v>389.99</v>
       </c>
-      <c r="E224" s="1">
+      <c r="E225" s="1">
         <v>356.87</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F225" s="1">
         <v>199.99</v>
       </c>
-    </row>
-    <row r="225" spans="1:6">
-      <c r="A225" t="s">
-        <v>230</v>
-      </c>
-      <c r="C225" s="1">
+      <c r="G225" s="1">
+        <v>379.13</v>
+      </c>
+      <c r="H225" s="1">
+        <v>128.39</v>
+      </c>
+      <c r="I225" s="1">
+        <v>409.99</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" t="s">
+        <v>234</v>
+      </c>
+      <c r="C226" s="1">
         <v>1239.13</v>
       </c>
-      <c r="D225" s="1">
+      <c r="D226" s="1">
         <v>678.42</v>
       </c>
-      <c r="E225" s="1">
+      <c r="E226" s="1">
         <v>642.64</v>
       </c>
-      <c r="F225" s="1">
+      <c r="F226" s="1">
         <v>169.98</v>
       </c>
-    </row>
-    <row r="226" spans="1:6">
-      <c r="A226" t="s">
-        <v>231</v>
-      </c>
-      <c r="C226" s="1">
+      <c r="G226" s="1">
+        <v>640.3</v>
+      </c>
+      <c r="H226" s="1">
+        <v>493.0699999999999</v>
+      </c>
+      <c r="I226" s="1">
+        <v>1477.2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" t="s">
+        <v>235</v>
+      </c>
+      <c r="C227" s="1">
         <v>144.99</v>
       </c>
-      <c r="D226" s="1">
+      <c r="D227" s="1">
         <v>712.8099999999999</v>
       </c>
-      <c r="E226" s="1">
+      <c r="E227" s="1">
         <v>1093.27</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F227" s="1">
         <v>197.57</v>
       </c>
-    </row>
-    <row r="227" spans="1:6">
-      <c r="A227" t="s">
-        <v>232</v>
-      </c>
-      <c r="C227" s="1">
+      <c r="G227" s="1">
+        <v>635.67</v>
+      </c>
+      <c r="H227" s="1">
+        <v>1364.8</v>
+      </c>
+      <c r="I227" s="1">
+        <v>219.58</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" t="s">
+        <v>236</v>
+      </c>
+      <c r="C228" s="1">
         <v>631.3900000000001</v>
       </c>
-      <c r="D227" s="1">
+      <c r="D228" s="1">
         <v>743.03</v>
       </c>
-      <c r="E227" s="1">
+      <c r="E228" s="1">
         <v>511.9000000000001</v>
       </c>
-      <c r="F227" s="1">
+      <c r="F228" s="1">
         <v>180</v>
       </c>
-    </row>
-    <row r="228" spans="1:6">
-      <c r="A228" t="s">
-        <v>233</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D228" s="1">
+      <c r="G228" s="1">
+        <v>144.78</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I228" s="1">
+        <v>302.58</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" t="s">
+        <v>237</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D229" s="1">
         <v>535.58</v>
       </c>
-      <c r="E228" s="1">
+      <c r="E229" s="1">
         <v>348.6500000000001</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F229" s="1">
         <v>622.58</v>
       </c>
-    </row>
-    <row r="229" spans="1:6">
-      <c r="A229" t="s">
-        <v>234</v>
-      </c>
-      <c r="C229" s="1">
+      <c r="G229" s="1">
+        <v>428.98</v>
+      </c>
+      <c r="H229" s="1">
+        <v>292.39</v>
+      </c>
+      <c r="I229" s="1">
+        <v>747.7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" t="s">
+        <v>238</v>
+      </c>
+      <c r="C230" s="1">
         <v>336.16</v>
       </c>
-      <c r="D229" s="1">
+      <c r="D230" s="1">
         <v>503.39</v>
       </c>
-      <c r="E229" s="1">
+      <c r="E230" s="1">
         <v>355.99</v>
       </c>
-      <c r="F229" s="1">
+      <c r="F230" s="1">
         <v>1044.48</v>
       </c>
-    </row>
-    <row r="230" spans="1:6">
-      <c r="A230" t="s">
-        <v>235</v>
-      </c>
-      <c r="C230" s="1">
+      <c r="G230" s="1">
+        <v>42.32</v>
+      </c>
+      <c r="H230" s="1">
+        <v>623.98</v>
+      </c>
+      <c r="I230" s="1">
+        <v>159.29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" t="s">
+        <v>239</v>
+      </c>
+      <c r="C231" s="1">
         <v>288.13</v>
       </c>
-      <c r="D230" s="1">
-        <v>623.67</v>
-      </c>
-      <c r="E230" s="1">
-        <v>935.1200000000001</v>
-      </c>
-      <c r="F230" s="1">
+      <c r="D231" s="1">
+        <v>623.6700000000001</v>
+      </c>
+      <c r="E231" s="1">
+        <v>935.12</v>
+      </c>
+      <c r="F231" s="1">
         <v>496.29</v>
       </c>
-    </row>
-    <row r="231" spans="1:6">
-      <c r="A231" t="s">
-        <v>236</v>
-      </c>
-      <c r="C231" s="1">
+      <c r="G231" s="1">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="H231" s="1">
+        <v>237.28</v>
+      </c>
+      <c r="I231" s="1">
+        <v>82.98999999999999</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" t="s">
+        <v>240</v>
+      </c>
+      <c r="C232" s="1">
         <v>1669.3</v>
       </c>
-      <c r="D231" s="1">
+      <c r="D232" s="1">
         <v>180</v>
       </c>
-      <c r="E231" s="1">
+      <c r="E232" s="1">
         <v>296.15</v>
       </c>
-      <c r="F231" s="1">
+      <c r="F232" s="1">
         <v>731.49</v>
       </c>
-    </row>
-    <row r="232" spans="1:6">
-      <c r="A232" t="s">
-        <v>237</v>
-      </c>
-      <c r="C232" s="1">
+      <c r="G232" s="1">
+        <v>707.9200000000001</v>
+      </c>
+      <c r="H232" s="1">
+        <v>997.8299999999999</v>
+      </c>
+      <c r="I232" s="1">
+        <v>966.5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" t="s">
+        <v>241</v>
+      </c>
+      <c r="C233" s="1">
         <v>1084.71</v>
       </c>
-      <c r="D232" s="1">
+      <c r="D233" s="1">
         <v>44.99</v>
       </c>
-      <c r="E232" s="1">
+      <c r="E233" s="1">
         <v>523.9400000000001</v>
       </c>
-      <c r="F232" s="1">
+      <c r="F233" s="1">
         <v>1143.47</v>
       </c>
-    </row>
-    <row r="233" spans="1:6">
-      <c r="A233" t="s">
-        <v>238</v>
-      </c>
-      <c r="C233" s="1">
+      <c r="G233" s="1">
+        <v>396.18</v>
+      </c>
+      <c r="H233" s="1">
+        <v>769.22</v>
+      </c>
+      <c r="I233" s="1">
+        <v>154.72</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" t="s">
+        <v>242</v>
+      </c>
+      <c r="C234" s="1">
         <v>84.98999999999999</v>
       </c>
-      <c r="D233" s="1">
+      <c r="D234" s="1">
         <v>1463.42</v>
       </c>
-      <c r="E233" s="1">
+      <c r="E234" s="1">
         <v>1159.75</v>
       </c>
-      <c r="F233" s="1">
-        <v>680.2900000000001</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6">
-      <c r="A234" t="s">
-        <v>239</v>
-      </c>
-      <c r="C234" s="1">
+      <c r="F234" s="1">
+        <v>680.29</v>
+      </c>
+      <c r="G234" s="1">
+        <v>1434.44</v>
+      </c>
+      <c r="H234" s="1">
+        <v>422.71</v>
+      </c>
+      <c r="I234" s="1">
+        <v>207.53</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" t="s">
+        <v>243</v>
+      </c>
+      <c r="C235" s="1">
         <v>526.53</v>
       </c>
-      <c r="D234" s="1">
+      <c r="D235" s="1">
         <v>302.66</v>
       </c>
-      <c r="E234" s="1">
+      <c r="E235" s="1">
         <v>80.98999999999999</v>
       </c>
-      <c r="F234" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6">
-      <c r="A235" t="s">
-        <v>240</v>
-      </c>
-      <c r="C235" s="1">
+      <c r="F235" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="1">
+        <v>707.54</v>
+      </c>
+      <c r="H235" s="1">
+        <v>330.26</v>
+      </c>
+      <c r="I235" s="1">
+        <v>286.76</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" t="s">
+        <v>244</v>
+      </c>
+      <c r="C236" s="1">
         <v>138.6</v>
       </c>
-      <c r="D235" s="1">
+      <c r="D236" s="1">
         <v>910.96</v>
       </c>
-      <c r="E235" s="1">
+      <c r="E236" s="1">
         <v>401.98</v>
       </c>
-      <c r="F235" s="1">
+      <c r="F236" s="1">
         <v>666.29</v>
       </c>
-    </row>
-    <row r="236" spans="1:6">
-      <c r="A236" t="s">
-        <v>241</v>
-      </c>
-      <c r="C236" s="1">
+      <c r="G236" s="1">
+        <v>1080.77</v>
+      </c>
+      <c r="H236" s="1">
+        <v>1348.93</v>
+      </c>
+      <c r="I236" s="1">
+        <v>78.29000000000001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" t="s">
+        <v>245</v>
+      </c>
+      <c r="C237" s="1">
         <v>78.3</v>
       </c>
-      <c r="D236" s="1">
+      <c r="D237" s="1">
         <v>131.98</v>
       </c>
-      <c r="E236" s="1">
+      <c r="E237" s="1">
         <v>757.96</v>
       </c>
-      <c r="F236" s="1">
+      <c r="F237" s="1">
         <v>375.39</v>
       </c>
-    </row>
-    <row r="237" spans="1:6">
-      <c r="A237" t="s">
-        <v>242</v>
-      </c>
-      <c r="C237" s="1">
-        <v>726.2</v>
-      </c>
-      <c r="D237" s="1">
+      <c r="G237" s="1">
+        <v>1035.58</v>
+      </c>
+      <c r="H237" s="1">
+        <v>364.41</v>
+      </c>
+      <c r="I237" s="1">
+        <v>470.47</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" t="s">
+        <v>246</v>
+      </c>
+      <c r="C238" s="1">
+        <v>726.1999999999998</v>
+      </c>
+      <c r="D238" s="1">
         <v>262.84</v>
       </c>
-      <c r="E237" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F237" s="1">
+      <c r="E238" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F238" s="1">
         <v>216.98</v>
       </c>
-    </row>
-    <row r="238" spans="1:6">
-      <c r="A238" t="s">
-        <v>243</v>
-      </c>
-      <c r="C238" s="1">
+      <c r="G238" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H238" s="1">
+        <v>156.75</v>
+      </c>
+      <c r="I238" s="1">
+        <v>297.97</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" t="s">
+        <v>247</v>
+      </c>
+      <c r="C239" s="1">
         <v>320.14</v>
       </c>
-      <c r="D238" s="1">
+      <c r="D239" s="1">
         <v>138.6</v>
       </c>
-      <c r="E238" s="1">
+      <c r="E239" s="1">
         <v>757.96</v>
       </c>
-      <c r="F238" s="1">
+      <c r="F239" s="1">
         <v>868.11</v>
       </c>
-    </row>
-    <row r="239" spans="1:6">
-      <c r="A239" t="s">
-        <v>244</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D239" s="1">
+      <c r="G239" s="1">
+        <v>708.78</v>
+      </c>
+      <c r="H239" s="1">
+        <v>798.46</v>
+      </c>
+      <c r="I239" s="1">
+        <v>811.5599999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" t="s">
+        <v>248</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240" s="1">
         <v>147.82</v>
       </c>
-      <c r="E239" s="1">
+      <c r="E240" s="1">
         <v>664.8</v>
       </c>
-      <c r="F239" s="1">
+      <c r="F240" s="1">
         <v>253.98</v>
       </c>
-    </row>
-    <row r="240" spans="1:6">
-      <c r="A240" t="s">
-        <v>245</v>
-      </c>
-      <c r="C240" s="1">
+      <c r="G240" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" s="1">
+        <v>718.97</v>
+      </c>
+      <c r="I240" s="1">
+        <v>1329.96</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" t="s">
+        <v>249</v>
+      </c>
+      <c r="C241" s="1">
         <v>823.99</v>
       </c>
-      <c r="D240" s="1">
+      <c r="D241" s="1">
         <v>405.88</v>
       </c>
-      <c r="E240" s="1">
+      <c r="E241" s="1">
         <v>960.9299999999999</v>
       </c>
-      <c r="F240" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
-      <c r="A241" t="s">
-        <v>246</v>
-      </c>
-      <c r="C241" s="1">
+      <c r="F241" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="1">
+        <v>178.97</v>
+      </c>
+      <c r="H241" s="1">
+        <v>217.06</v>
+      </c>
+      <c r="I241" s="1">
+        <v>121.98</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" t="s">
+        <v>250</v>
+      </c>
+      <c r="C242" s="1">
         <v>195.25</v>
       </c>
-      <c r="D241" s="1">
+      <c r="D242" s="1">
         <v>478.55</v>
       </c>
-      <c r="E241" s="1">
+      <c r="E242" s="1">
         <v>401.29</v>
       </c>
-      <c r="F241" s="1">
+      <c r="F242" s="1">
         <v>1017.54</v>
       </c>
-    </row>
-    <row r="242" spans="1:6">
-      <c r="A242" t="s">
-        <v>247</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D242" s="1">
+      <c r="G242" s="1">
+        <v>1314.79</v>
+      </c>
+      <c r="H242" s="1">
+        <v>44.99</v>
+      </c>
+      <c r="I242" s="1">
+        <v>591.87</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" t="s">
+        <v>251</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D243" s="1">
         <v>634.28</v>
       </c>
-      <c r="E242" s="1">
+      <c r="E243" s="1">
         <v>762.26</v>
       </c>
-      <c r="F242" s="1">
+      <c r="F243" s="1">
         <v>1166.55</v>
       </c>
-    </row>
-    <row r="243" spans="1:6">
-      <c r="A243" t="s">
-        <v>248</v>
-      </c>
-      <c r="C243" s="1">
+      <c r="G243" s="1">
+        <v>952.75</v>
+      </c>
+      <c r="H243" s="1">
+        <v>1058.7</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" t="s">
+        <v>252</v>
+      </c>
+      <c r="C244" s="1">
         <v>1353.99</v>
       </c>
-      <c r="D243" s="1">
+      <c r="D244" s="1">
         <v>802.9100000000001</v>
       </c>
-      <c r="E243" s="1">
+      <c r="E244" s="1">
         <v>1638.57</v>
       </c>
-      <c r="F243" s="1">
+      <c r="F244" s="1">
         <v>550.7</v>
       </c>
-    </row>
-    <row r="244" spans="1:6">
-      <c r="A244" t="s">
-        <v>249</v>
-      </c>
-      <c r="C244" s="1">
-        <v>923.73</v>
-      </c>
-      <c r="D244" s="1">
+      <c r="G244" s="1">
+        <v>2027</v>
+      </c>
+      <c r="H244" s="1">
+        <v>1590.15</v>
+      </c>
+      <c r="I244" s="1">
+        <v>900.85</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" t="s">
+        <v>253</v>
+      </c>
+      <c r="C245" s="1">
+        <v>923.7299999999999</v>
+      </c>
+      <c r="D245" s="1">
         <v>1344.49</v>
       </c>
-      <c r="E244" s="1">
+      <c r="E245" s="1">
         <v>38.83</v>
       </c>
-      <c r="F244" s="1">
+      <c r="F245" s="1">
         <v>659.96</v>
       </c>
-    </row>
-    <row r="245" spans="1:6">
-      <c r="A245" t="s">
-        <v>250</v>
-      </c>
-      <c r="C245" s="1">
+      <c r="G245" s="1">
+        <v>1471.85</v>
+      </c>
+      <c r="H245" s="1">
+        <v>398.59</v>
+      </c>
+      <c r="I245" s="1">
+        <v>1082.18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" t="s">
+        <v>254</v>
+      </c>
+      <c r="C246" s="1">
         <v>1039.53</v>
       </c>
-      <c r="D245" s="1">
+      <c r="D246" s="1">
         <v>672</v>
       </c>
-      <c r="E245" s="1">
+      <c r="E246" s="1">
         <v>75.73999999999999</v>
       </c>
-      <c r="F245" s="1">
+      <c r="F246" s="1">
         <v>506.78</v>
       </c>
-    </row>
-    <row r="246" spans="1:6">
-      <c r="A246" t="s">
-        <v>251</v>
-      </c>
-      <c r="C246" s="1">
+      <c r="G246" s="1">
+        <v>542.78</v>
+      </c>
+      <c r="H246" s="1">
+        <v>1609.08</v>
+      </c>
+      <c r="I246" s="1">
+        <v>957.9200000000001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" t="s">
+        <v>255</v>
+      </c>
+      <c r="C247" s="1">
         <v>1367.25</v>
       </c>
-      <c r="D246" s="1">
+      <c r="D247" s="1">
         <v>1282.76</v>
       </c>
-      <c r="E246" s="1">
+      <c r="E247" s="1">
         <v>1494.11</v>
       </c>
-      <c r="F246" s="1">
-        <v>3784.309999999999</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6">
-      <c r="A247" t="s">
-        <v>252</v>
-      </c>
-      <c r="C247" s="1">
+      <c r="F247" s="1">
+        <v>3784.31</v>
+      </c>
+      <c r="G247" s="1">
+        <v>3592.49</v>
+      </c>
+      <c r="H247" s="1">
+        <v>4891.530000000001</v>
+      </c>
+      <c r="I247" s="1">
+        <v>2364.76</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" t="s">
+        <v>256</v>
+      </c>
+      <c r="C248" s="1">
         <v>446.99</v>
       </c>
-      <c r="D247" s="1">
+      <c r="D248" s="1">
         <v>231.98</v>
       </c>
-      <c r="E247" s="1">
+      <c r="E248" s="1">
         <v>237.16</v>
       </c>
-      <c r="F247" s="1">
+      <c r="F248" s="1">
         <v>189.99</v>
       </c>
-    </row>
-    <row r="248" spans="1:6">
-      <c r="A248" t="s">
-        <v>253</v>
-      </c>
-      <c r="C248" s="1">
-        <v>2761.339999999999</v>
-      </c>
-      <c r="D248" s="1">
+      <c r="G248" s="1">
+        <v>728.0599999999999</v>
+      </c>
+      <c r="H248" s="1">
+        <v>198.98</v>
+      </c>
+      <c r="I248" s="1">
+        <v>894.9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" t="s">
+        <v>257</v>
+      </c>
+      <c r="C249" s="1">
+        <v>2761.34</v>
+      </c>
+      <c r="D249" s="1">
         <v>2104.6</v>
       </c>
-      <c r="E248" s="1">
+      <c r="E249" s="1">
         <v>1534.81</v>
       </c>
-      <c r="F248" s="1">
+      <c r="F249" s="1">
         <v>1488.68</v>
       </c>
-    </row>
-    <row r="249" spans="1:6">
-      <c r="A249" t="s">
-        <v>254</v>
-      </c>
-      <c r="C249" s="1">
+      <c r="G249" s="1">
+        <v>1086.16</v>
+      </c>
+      <c r="H249" s="1">
+        <v>2470.74</v>
+      </c>
+      <c r="I249" s="1">
+        <v>1128.62</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" t="s">
+        <v>258</v>
+      </c>
+      <c r="C250" s="1">
         <v>364.79</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E249" s="1">
+      <c r="D250" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E250" s="1">
         <v>288.13</v>
       </c>
-      <c r="F249" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250" t="s">
-        <v>255</v>
-      </c>
-      <c r="C250" s="1">
+      <c r="F250" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="1">
+        <v>674.97</v>
+      </c>
+      <c r="H250" s="1">
+        <v>280.55</v>
+      </c>
+      <c r="I250" s="1">
+        <v>390.21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" t="s">
+        <v>259</v>
+      </c>
+      <c r="C251" s="1">
         <v>628.04</v>
       </c>
-      <c r="D250" s="1">
+      <c r="D251" s="1">
         <v>615.9299999999999</v>
       </c>
-      <c r="E250" s="1">
+      <c r="E251" s="1">
         <v>1451.76</v>
       </c>
-      <c r="F250" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251" t="s">
-        <v>256</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D251" s="1">
+      <c r="F251" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G251" s="1">
+        <v>-323</v>
+      </c>
+      <c r="H251" s="1">
+        <v>642.11</v>
+      </c>
+      <c r="I251" s="1">
+        <v>348.98</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" t="s">
+        <v>260</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D252" s="1">
         <v>180</v>
       </c>
-      <c r="E251" s="1">
+      <c r="E252" s="1">
         <v>159.98</v>
       </c>
-      <c r="F251" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6">
-      <c r="A252" t="s">
-        <v>257</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D252" s="1">
+      <c r="F252" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G252" s="1">
+        <v>49.43</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I252" s="1">
+        <v>131.59</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" t="s">
+        <v>261</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D253" s="1">
         <v>153.99</v>
       </c>
-      <c r="E252" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F252" s="1">
+      <c r="E253" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="1">
         <v>288.13</v>
       </c>
-    </row>
-    <row r="253" spans="1:6">
-      <c r="A253" t="s">
-        <v>258</v>
-      </c>
-      <c r="C253" s="1">
+      <c r="G253" s="1">
+        <v>191.99</v>
+      </c>
+      <c r="H253" s="1">
+        <v>291.98</v>
+      </c>
+      <c r="I253" s="1">
+        <v>581.8399999999999</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" t="s">
+        <v>262</v>
+      </c>
+      <c r="C254" s="1">
         <v>620.29</v>
       </c>
-      <c r="D253" s="1">
+      <c r="D254" s="1">
         <v>1773.31</v>
       </c>
-      <c r="E253" s="1">
+      <c r="E254" s="1">
         <v>1061.06</v>
       </c>
-      <c r="F253" s="1">
-        <v>689.8900000000001</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6">
-      <c r="A254" t="s">
-        <v>259</v>
-      </c>
-      <c r="C254" s="1">
+      <c r="F254" s="1">
+        <v>689.89</v>
+      </c>
+      <c r="G254" s="1">
+        <v>360.19</v>
+      </c>
+      <c r="H254" s="1">
+        <v>646.03</v>
+      </c>
+      <c r="I254" s="1">
+        <v>965.37</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" t="s">
+        <v>263</v>
+      </c>
+      <c r="C255" s="1">
         <v>426.86</v>
       </c>
-      <c r="D254" s="1">
+      <c r="D255" s="1">
         <v>406.19</v>
       </c>
-      <c r="E254" s="1">
+      <c r="E255" s="1">
         <v>-341.98</v>
       </c>
-      <c r="F254" s="1">
+      <c r="F255" s="1">
         <v>884.86</v>
       </c>
-    </row>
-    <row r="255" spans="1:6">
-      <c r="A255" t="s">
-        <v>260</v>
-      </c>
-      <c r="C255" s="1">
+      <c r="G255" s="1">
+        <v>476.65</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I255" s="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" t="s">
+        <v>264</v>
+      </c>
+      <c r="C256" s="1">
         <v>1085</v>
       </c>
-      <c r="D255" s="1">
+      <c r="D256" s="1">
         <v>256.9</v>
       </c>
-      <c r="E255" s="1">
+      <c r="E256" s="1">
         <v>528.88</v>
       </c>
-      <c r="F255" s="1">
-        <v>-45.59999999999999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6">
-      <c r="A256" t="s">
-        <v>261</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D256" s="1">
+      <c r="F256" s="1">
+        <v>-45.59999999999998</v>
+      </c>
+      <c r="G256" s="1">
+        <v>998.5700000000001</v>
+      </c>
+      <c r="H256" s="1">
+        <v>367.89</v>
+      </c>
+      <c r="I256" s="1">
+        <v>342.49</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" t="s">
+        <v>265</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D257" s="1">
         <v>202.99</v>
       </c>
-      <c r="E256" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F256" s="1">
+      <c r="E257" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F257" s="1">
         <v>329.99</v>
       </c>
-    </row>
-    <row r="257" spans="1:6">
-      <c r="A257" t="s">
-        <v>262</v>
-      </c>
-      <c r="C257" s="1">
+      <c r="G257" s="1">
+        <v>380.31</v>
+      </c>
+      <c r="H257" s="1">
+        <v>556.97</v>
+      </c>
+      <c r="I257" s="1">
+        <v>372.62</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" t="s">
+        <v>266</v>
+      </c>
+      <c r="C258" s="1">
         <v>365.96</v>
       </c>
-      <c r="D257" s="1">
+      <c r="D258" s="1">
         <v>172.99</v>
       </c>
-      <c r="E257" s="1">
+      <c r="E258" s="1">
         <v>45.99</v>
       </c>
-      <c r="F257" s="1">
+      <c r="F258" s="1">
         <v>784.51</v>
       </c>
-    </row>
-    <row r="258" spans="1:6">
-      <c r="A258" t="s">
-        <v>263</v>
-      </c>
-      <c r="C258" s="1">
+      <c r="G258" s="1">
+        <v>516.28</v>
+      </c>
+      <c r="H258" s="1">
+        <v>1343.78</v>
+      </c>
+      <c r="I258" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" t="s">
+        <v>267</v>
+      </c>
+      <c r="C259" s="1">
         <v>538.96</v>
       </c>
-      <c r="D258" s="1">
+      <c r="D259" s="1">
         <v>1418.94</v>
       </c>
-      <c r="E258" s="1">
-        <v>849.53</v>
-      </c>
-      <c r="F258" s="1">
-        <v>514.8</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
-      <c r="A259" t="s">
-        <v>264</v>
-      </c>
-      <c r="C259" s="1">
+      <c r="E259" s="1">
+        <v>849.5300000000001</v>
+      </c>
+      <c r="F259" s="1">
+        <v>514.8000000000001</v>
+      </c>
+      <c r="G259" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="H259" s="1">
+        <v>785.6999999999998</v>
+      </c>
+      <c r="I259" s="1">
+        <v>608.79</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" t="s">
+        <v>268</v>
+      </c>
+      <c r="C260" s="1">
         <v>427.37</v>
       </c>
-      <c r="D259" s="1">
+      <c r="D260" s="1">
         <v>220.5</v>
       </c>
-      <c r="E259" s="1">
+      <c r="E260" s="1">
         <v>46.91</v>
       </c>
-      <c r="F259" s="1">
+      <c r="F260" s="1">
         <v>1119.75</v>
       </c>
-    </row>
-    <row r="260" spans="1:6">
-      <c r="A260" t="s">
-        <v>265</v>
-      </c>
-      <c r="C260" s="1">
+      <c r="G260" s="1">
+        <v>206.68</v>
+      </c>
+      <c r="H260" s="1">
+        <v>1248.36</v>
+      </c>
+      <c r="I260" s="1">
+        <v>1651.55</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" t="s">
+        <v>269</v>
+      </c>
+      <c r="C261" s="1">
         <v>1349.88</v>
       </c>
-      <c r="D260" s="1">
+      <c r="D261" s="1">
         <v>1189.33</v>
       </c>
-      <c r="E260" s="1">
+      <c r="E261" s="1">
         <v>1288.49</v>
       </c>
-      <c r="F260" s="1">
+      <c r="F261" s="1">
         <v>1955.66</v>
       </c>
-    </row>
-    <row r="261" spans="1:6">
-      <c r="A261" t="s">
-        <v>266</v>
-      </c>
-      <c r="C261" s="1">
+      <c r="G261" s="1">
+        <v>802.22</v>
+      </c>
+      <c r="H261" s="1">
+        <v>1865.27</v>
+      </c>
+      <c r="I261" s="1">
+        <v>1513.06</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" t="s">
+        <v>270</v>
+      </c>
+      <c r="C262" s="1">
         <v>130.48</v>
       </c>
-      <c r="D261" s="1">
+      <c r="D262" s="1">
         <v>158.28</v>
       </c>
-      <c r="E261" s="1">
+      <c r="E262" s="1">
         <v>234.57</v>
       </c>
-      <c r="F261" s="1">
-        <v>934.8599999999999</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
-      <c r="A262" t="s">
-        <v>267</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D262" s="1">
+      <c r="F262" s="1">
+        <v>934.86</v>
+      </c>
+      <c r="G262" s="1">
+        <v>999.05</v>
+      </c>
+      <c r="H262" s="1">
+        <v>2231.56</v>
+      </c>
+      <c r="I262" s="1">
+        <v>634.39</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" t="s">
+        <v>271</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D263" s="1">
         <v>1051.87</v>
       </c>
-      <c r="E262" s="1">
+      <c r="E263" s="1">
         <v>354.99</v>
       </c>
-      <c r="F262" s="1">
+      <c r="F263" s="1">
         <v>90.98</v>
       </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263" t="s">
-        <v>268</v>
-      </c>
-      <c r="C263" s="1">
+      <c r="G263" s="1">
+        <v>999.49</v>
+      </c>
+      <c r="H263" s="1">
+        <v>1139.96</v>
+      </c>
+      <c r="I263" s="1">
+        <v>189.99</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" t="s">
+        <v>272</v>
+      </c>
+      <c r="C264" s="1">
         <v>2923.99</v>
       </c>
-      <c r="D263" s="1">
+      <c r="D264" s="1">
         <v>1428.06</v>
       </c>
-      <c r="E263" s="1">
+      <c r="E264" s="1">
         <v>2019.4</v>
       </c>
-      <c r="F263" s="1">
-        <v>338.1900000000001</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264" t="s">
-        <v>269</v>
-      </c>
-      <c r="C264" s="1">
+      <c r="F264" s="1">
+        <v>338.19</v>
+      </c>
+      <c r="G264" s="1">
+        <v>2434.09</v>
+      </c>
+      <c r="H264" s="1">
+        <v>2221.03</v>
+      </c>
+      <c r="I264" s="1">
+        <v>3112.18</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" t="s">
+        <v>273</v>
+      </c>
+      <c r="C265" s="1">
         <v>449.67</v>
       </c>
-      <c r="D264" s="1">
+      <c r="D265" s="1">
         <v>1409.01</v>
       </c>
-      <c r="E264" s="1">
+      <c r="E265" s="1">
         <v>1886.74</v>
       </c>
-      <c r="F264" s="1">
+      <c r="F265" s="1">
         <v>2366.12</v>
       </c>
-    </row>
-    <row r="265" spans="1:6">
-      <c r="A265" t="s">
-        <v>270</v>
-      </c>
-      <c r="C265" s="1">
+      <c r="G265" s="1">
+        <v>1175.58</v>
+      </c>
+      <c r="H265" s="1">
+        <v>1929.97</v>
+      </c>
+      <c r="I265" s="1">
+        <v>162.18</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" t="s">
+        <v>274</v>
+      </c>
+      <c r="C266" s="1">
         <v>827.1</v>
       </c>
-      <c r="D265" s="1">
+      <c r="D266" s="1">
         <v>618.0700000000001</v>
       </c>
-      <c r="E265" s="1">
+      <c r="E266" s="1">
         <v>1655.62</v>
       </c>
-      <c r="F265" s="1">
+      <c r="F266" s="1">
         <v>1463.27</v>
       </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266" t="s">
-        <v>271</v>
-      </c>
-      <c r="C266" s="1">
+      <c r="G266" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H266" s="1">
+        <v>388.98</v>
+      </c>
+      <c r="I266" s="1">
+        <v>209.99</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" t="s">
+        <v>275</v>
+      </c>
+      <c r="C267" s="1">
         <v>1247.04</v>
       </c>
-      <c r="D266" s="1">
+      <c r="D267" s="1">
         <v>524.9</v>
       </c>
-      <c r="E266" s="1">
+      <c r="E267" s="1">
         <v>1229.05</v>
       </c>
-      <c r="F266" s="1">
+      <c r="F267" s="1">
         <v>651.26</v>
       </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267" t="s">
-        <v>272</v>
-      </c>
-      <c r="C267" s="1">
+      <c r="G267" s="1">
+        <v>258.29</v>
+      </c>
+      <c r="H267" s="1">
+        <v>827.75</v>
+      </c>
+      <c r="I267" s="1">
+        <v>1358.8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" t="s">
+        <v>276</v>
+      </c>
+      <c r="C268" s="1">
         <v>639</v>
       </c>
-      <c r="D267" s="1">
+      <c r="D268" s="1">
         <v>183.11</v>
       </c>
-      <c r="E267" s="1">
+      <c r="E268" s="1">
         <v>241.03</v>
       </c>
-      <c r="F267" s="1">
+      <c r="F268" s="1">
         <v>203.98</v>
       </c>
+      <c r="G268" s="1">
+        <v>44.99</v>
+      </c>
+      <c r="H268" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="266">
+  <mergeCells count="267">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -6016,6 +8457,7 @@
     <mergeCell ref="A265:B265"/>
     <mergeCell ref="A266:B266"/>
     <mergeCell ref="A267:B267"/>
+    <mergeCell ref="A268:B268"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
